--- a/docs/testing_checklist.xlsx
+++ b/docs/testing_checklist.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.5" customWidth="1" min="1" max="1"/>
@@ -590,7 +590,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Ops Reservist - Testing Checklist</t>
+          <t>ReservistGO - Testing Checklist</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Session cleared, returned to login screen, no state persists</t>
+          <t>Confirmation dialog appears. On confirm: session cleared, returned to login screen, no state persists</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -798,17 +798,17 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Session expiry warning</t>
+          <t>Idle warning (18 min)</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Wait 55 minutes after login without refreshing the session</t>
+          <t>Leave the app idle for 18 minutes without interaction</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Banner shown: "Your session is about to expire." Tap to stay logged in resets the timer</t>
+          <t>Warning banner appears: idle warning shown with option to stay. Session has not yet ended</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Self-signup - new user</t>
+          <t>Session expiry warning</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Sign up with a valid name, Singapore number (starts 6/8/9, 8 digits), and password (min 6 chars)</t>
+          <t>Wait 55 minutes after login without refreshing the session</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Screen shows "Your request has been submitted." Auth account is created. Pending signup appears in admin inbox labelled New</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Banner shown: "Your session is about to expire." Tap to stay logged in resets the timer</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr"/>
@@ -856,22 +856,22 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Signup - invalid contact</t>
+          <t>Tab persistence</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Attempt signup with a contact that does not start with 6, 8, or 9, or has wrong digit count</t>
+          <t>Close and reopen the browser tab before the session expires</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Error: "Contact must be an 8-digit Singapore number." No account created</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>User is still logged in. Session state is restored from sessionStorage. No re-login required</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr"/>
@@ -885,22 +885,22 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Signup - short password</t>
+          <t>Self-signup - new user</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Attempt signup with a password under 6 characters</t>
+          <t>Sign up with a valid name, Singapore number (starts 6/8/9, 8 digits), and password (min 6 chars)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Error: "Password must be at least 6 characters." No account created</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
+          <t>Screen shows "Your request has been submitted." Auth account is created. Pending signup appears in admin inbox labelled New</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr"/>
@@ -914,17 +914,17 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Signup - already pending</t>
+          <t>Signup - invalid contact</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Attempt signup again for a contact that already has a pending signup request</t>
+          <t>Attempt signup with a contact that does not start with 6, 8, or 9, or has wrong digit count</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Error: "A signup request for this number is already pending admin approval."</t>
+          <t>Error: "Contact must be an 8-digit Singapore number." No account created</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -943,22 +943,22 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Signup - rejected contact</t>
+          <t>Signup - short password</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Attempt signup with a contact that was previously rejected</t>
+          <t>Attempt signup with a password under 6 characters</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Error: "Your previous signup request was not approved. Contact your supervisor."</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Error: "Password must be at least 6 characters." No account created</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr"/>
@@ -972,22 +972,22 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Signup - outside active cycle</t>
+          <t>Signup - already pending</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Attempt signup when no cycle is currently live</t>
+          <t>Attempt signup again for a contact that already has a pending signup request</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Error: "No active intake batch is open for sign-up right now."</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
+          <t>Error: "A signup request for this number is already pending admin approval."</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr"/>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Login - inactive account</t>
+          <t>Signup - rejected contact</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Log in with a valid contact that belongs to an inactive (deactivated) reservist</t>
+          <t>Attempt signup with a contact that was previously rejected</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Re-enrollment request auto-submitted. Error shown: "Your account is inactive... A re-enrollment request has been sent."</t>
+          <t>Error: "Your previous signup request was not approved. Contact your supervisor."</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -1030,22 +1030,22 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Demo - reservist mode</t>
+          <t>Signup - outside active cycle</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Tap "Try as Reservist" on the login screen</t>
+          <t>Attempt signup when no cycle is currently live</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Logged in as Demo User with 4 demo personnel. Check-in tab is active. No DB calls are made</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Error: "No active intake batch is open for sign-up right now."</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr"/>
@@ -1059,118 +1059,118 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Demo - admin mode</t>
+          <t>Login - inactive account</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Tap "Try as Supervisor" on the login screen</t>
+          <t>Log in with a valid contact that belongs to an inactive (deactivated) reservist</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Logged in as Supervisor with demo attendance data. Overview tab is active. No DB calls are made</t>
-        </is>
-      </c>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Re-enrollment request auto-submitted. Error shown: "Your account is inactive... A re-enrollment request has been sent."</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr"/>
       <c r="G19" s="10" t="inlineStr"/>
     </row>
-    <row r="20" ht="6" customHeight="1"/>
-    <row r="21" ht="13.5" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. CHECK-IN - RESERVIST</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="27" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>GPS verification</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Tap Verify Location while physically within the HQ radius</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Status changes to "Verified" with green indicator. Distance from HQ is shown</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr"/>
-      <c r="G22" s="10" t="inlineStr"/>
-    </row>
-    <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>GPS out of range</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Tap Verify Location while outside the HQ radius</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Status shows "Out of range" with distance displayed. Check-in button is not available</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr"/>
-      <c r="G23" s="13" t="inlineStr"/>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Demo - reservist mode</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Tap "Try as Reservist" on the login screen</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Logged in as Demo User with 4 demo personnel. Check-in tab is active. No DB calls are made</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr"/>
+      <c r="G20" s="13" t="inlineStr"/>
+    </row>
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Demo - admin mode</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Tap "Try as Supervisor" on the login screen</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Logged in as Supervisor with demo attendance data. Overview tab is active. No DB calls are made</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr"/>
+      <c r="G21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22" ht="6" customHeight="1"/>
+    <row r="23" ht="13.5" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. CHECK-IN - OPS SECURITY (4 PHASES)</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
     </row>
     <row r="24" ht="27" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Phase 1 check-in</t>
+          <t>GPS verification</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>With GPS verified, tap the Check In button for Phase 1</t>
+          <t>Tap Verify Location while physically within the HQ radius</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Toast: "Checked in." Status card updates. Time and distance are recorded. Phase 2 tile becomes available</t>
+          <t>Status changes to "Verified" with green indicator. Distance from HQ is shown</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
@@ -1184,22 +1184,22 @@
     <row r="25" ht="27" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Phase prerequisite enforcement</t>
+          <t>GPS out of range</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Attempt Phase 3 (Return) before Phase 2 (Lunch out) has been logged</t>
+          <t>Tap Verify Location while outside the HQ radius</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Error toast: "Record your break out first." Phase 3 is not submitted</t>
+          <t>Status shows "Out of range" with distance displayed. Check-in button is not available</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -1213,22 +1213,22 @@
     <row r="26" ht="27" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>All 4 phases complete</t>
+          <t>Phase 1 check-in</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Submit all four phases in order within a single day</t>
+          <t>With GPS verified, tap the Check In button for Phase 1</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Completion card shown. All phase times are visible. Status is "Present". Meal eligibility updates if applicable</t>
+          <t>Toast: "Checked in." Status card updates. Time and distance are recorded. Phase 2 tile becomes available</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -1242,22 +1242,22 @@
     <row r="27" ht="27" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>GPS bypass check-in</t>
+          <t>Phase outside time window</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Use the "No GPS" bypass option to check in without GPS verification</t>
+          <t>View the check-in screen when the current time is outside all phase windows</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Check-in recorded. Attendance record is flagged as GPS bypassed in the log. Distance is null</t>
+          <t>Phase tile is visible but the action button is greyed out and cannot be tapped. No error occurs</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
@@ -1271,27 +1271,27 @@
     <row r="28" ht="27" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Late check-in warning (30 min)</t>
+          <t>Phase prerequisite enforcement</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Check in between 09:30 and 10:00 (30-60 min late)</t>
+          <t>Attempt Phase 3 (Return) before Phase 2 (Lunch out) has been logged</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Warning banner appears: "You are checking in late." Banner can be dismissed</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
+          <t>Error toast: "Record your break out first." Phase 3 is not submitted</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr"/>
@@ -1300,22 +1300,22 @@
     <row r="29" ht="27" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Late check-in reason (1 hour)</t>
+          <t>All 4 phases complete</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Check in after 10:00 (more than 60 min late)</t>
+          <t>Submit all four phases in order within a single day</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Reason modal opens automatically. Reason is required. Saved reason is visible in the admin log alongside a late flag</t>
+          <t>Completion card shown. All phase times are visible. Status is "Present". Meal eligibility updates if applicable</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -1329,27 +1329,27 @@
     <row r="30" ht="27" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Check-in before cycle start</t>
+          <t>GPS bypass trigger</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Attempt to check in when today is before the reservist's batch start date</t>
+          <t>Tap Verify Location and fail GPS 5 consecutive times</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Error: "Your reporting period has not started yet." No record is created</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>After the 5th failure, a "No GPS" bypass option appears. Before 5 failures, the bypass is not shown</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr"/>
@@ -1358,27 +1358,27 @@
     <row r="31" ht="27" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Check-in after cycle end</t>
+          <t>GPS bypass check-in</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Attempt to check in when today is after the reservist's batch end date</t>
+          <t>Use the "No GPS" bypass option to check in without GPS verification</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Error: "Your reporting period has ended." No record is created</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Check-in recorded. Attendance record is flagged as GPS bypassed in the log. Distance is null</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr"/>
@@ -1387,27 +1387,27 @@
     <row r="32" ht="27" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Offline check-in</t>
+          <t>Late check-in warning (30 min)</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Enable airplane mode, then check in with GPS verified</t>
+          <t>Check in between 09:30 and 10:00 (30-60 min late)</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Toast: "Checked in." Offline badge appears. On reconnection, the queued action is synced automatically and the badge disappears</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Warning banner appears: "You are checking in late." Banner can be dismissed</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr"/>
@@ -1416,27 +1416,27 @@
     <row r="33" ht="27" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Offline queue retry limit</t>
+          <t>Late check-in reason (1 hour)</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Simulate 3 failed sync attempts for a queued item (requires mocking a DB error)</t>
+          <t>Check in after 10:00 (more than 60 min late)</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>After 3 failures the item is dropped from the queue. User is notified via error toast on each failed attempt</t>
-        </is>
-      </c>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
+          <t>Reason modal opens automatically. Reason is required. Saved reason is visible in the admin log alongside a late flag</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr"/>
@@ -1445,22 +1445,22 @@
     <row r="34" ht="27" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Deactivated account check-in</t>
+          <t>Check-in before cycle start</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Attempt to check in with a user whose is_active flag is false</t>
+          <t>Attempt to check in when today is before the reservist's batch start date</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Error: "Your account has been deactivated. Please contact your supervisor."</t>
+          <t>Error: "Your reporting period has not started yet." No record is created</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -1474,27 +1474,27 @@
     <row r="35" ht="27" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>No-report day - check-in screen</t>
+          <t>Check-in after cycle end</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Log in on a day that has been marked as a no-reporting day</t>
+          <t>Attempt to check in when today is after the reservist's batch end date</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Check-in status shows "No reporting" with correct label. Phase tiles are hidden. No check-in is possible</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
+          <t>Error: "Your reporting period has ended." No record is created</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr"/>
@@ -1503,181 +1503,181 @@
     <row r="36" ht="27" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Weekend check-in screen</t>
+          <t>Offline check-in</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Open the app on a Saturday or Sunday</t>
+          <t>Enable airplane mode, then check in with GPS verified</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Status shows "Weekend - No reporting required." No phases displayed</t>
-        </is>
-      </c>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
+          <t>Toast: "Checked in." Offline badge appears. On reconnection, the queued action is synced automatically and the badge disappears</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr"/>
       <c r="G36" s="10" t="inlineStr"/>
     </row>
-    <row r="37" ht="6" customHeight="1"/>
-    <row r="38" ht="13.5" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. LEAVE AND MC REQUESTS</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
+    <row r="37" ht="27" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Offline queue retry limit</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Simulate 3 failed sync attempts for a queued item (requires mocking a DB error)</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>After 3 failures the item is dropped from the queue. User is notified via error toast on each failed attempt</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr"/>
+      <c r="G37" s="13" t="inlineStr"/>
+    </row>
+    <row r="38" ht="27" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Deactivated account check-in</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Attempt to check in with a user whose is_active flag is false</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Error: "Your account has been deactivated. Please contact your supervisor."</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr"/>
+      <c r="G38" s="10" t="inlineStr"/>
     </row>
     <row r="39" ht="27" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Submit leave request</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Submit an MC or leave request for a future date within the current cycle</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Toast: "Request submitted for approval." Request appears in history as Pending. Admin inbox shows the new request</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>No-report day - check-in screen</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>Log in on a day that has been marked as a no-reporting day</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>Check-in status shows "No reporting" with correct label. Phase tiles are hidden. No check-in is possible</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr"/>
-      <c r="G39" s="10" t="inlineStr"/>
+      <c r="G39" s="13" t="inlineStr"/>
     </row>
     <row r="40" ht="27" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>Submit request - already pending</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>Attempt to submit a second leave request while one is already pending</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>Error: "You already have a pending request." No second request is created</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Weekend check-in screen</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Open the app on a Saturday or Sunday</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Status shows "Weekend - No reporting required." No phases displayed</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr"/>
-      <c r="G40" s="13" t="inlineStr"/>
-    </row>
-    <row r="41" ht="27" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Submit request - past date</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Attempt to submit a leave request for a date before today</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Error: "Cannot submit a request for a past date." No request is created</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr"/>
-      <c r="G41" s="10" t="inlineStr"/>
-    </row>
-    <row r="42" ht="27" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>Submit request - outside cycle</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>Attempt to submit a leave request for a date outside the reservist's batch start and end dates</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>Error: "The selected date is outside your current cycle."</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr"/>
-      <c r="G42" s="13" t="inlineStr"/>
+      <c r="G40" s="10" t="inlineStr"/>
+    </row>
+    <row r="41" ht="6" customHeight="1"/>
+    <row r="42" ht="13.5" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. CHECK-IN - CAS / CRIME ALERT (2 PHASES)</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
     </row>
     <row r="43" ht="27" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Submit request - duplicate date</t>
+          <t>CAS - Phase 1 check-in</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Submit a request for a date that already has a non-cancelled, non-rejected request</t>
+          <t>Log in as a CAS reservist and tap Verify Location, then Check In for Phase 1</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Error: "You already submitted a request for this date." No duplicate is created</t>
+          <t>GPS verified. Check-in recorded with timestamp and distance. Phase 2 tile becomes available</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -1691,22 +1691,22 @@
     <row r="44" ht="27" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Cancel pending request</t>
+          <t>CAS - Phase 2 check-out</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Cancel a pending leave request before the admin has reviewed it</t>
+          <t>After Phase 1 is recorded, tap Check Out for Phase 2</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Toast: "Request cancelled." Status in history changes to Cancelled. DB record status is updated. Pending request badge clears</t>
+          <t>Phase 2 timestamp recorded. Completion card shown. Status is "Present"</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -1720,22 +1720,22 @@
     <row r="45" ht="27" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Cancel already-reviewed request</t>
+          <t>CAS - phases 3 and 4 absent</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Attempt to cancel a request that an admin has already approved or rejected</t>
+          <t>Log in as a CAS reservist and inspect the check-in screen</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Error: "Request was already reviewed by an admin." History reloads to show the current status</t>
+          <t>Only 2 phase tiles are visible (Check In and Check Out). Lunch out and Return tiles are not shown</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -1746,160 +1746,160 @@
       <c r="F45" s="9" t="inlineStr"/>
       <c r="G45" s="10" t="inlineStr"/>
     </row>
-    <row r="46" ht="27" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>Admin - approve MC leave</t>
-        </is>
-      </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>Admin approves an MC leave request from the Requests inbox</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>Request moves to Approved. Attendance record for that date is updated to MC. If the date is today, the roster updates immediately</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F46" s="9" t="inlineStr"/>
-      <c r="G46" s="13" t="inlineStr"/>
-    </row>
-    <row r="47" ht="27" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>3.9</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Admin - reject leave with reason</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>Admin rejects a leave request and provides a written reason</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Request moves to Rejected. Rejection reason is recorded. Reservist sees the rejection in their history</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F47" s="9" t="inlineStr"/>
-      <c r="G47" s="10" t="inlineStr"/>
+    <row r="46" ht="6" customHeight="1"/>
+    <row r="47" ht="13.5" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. LEAVE AND MC REQUESTS</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
     </row>
     <row r="48" ht="27" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="B48" s="12" t="inlineStr">
-        <is>
-          <t>Admin - bulk approve leaves</t>
-        </is>
-      </c>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>Select 3 pending leave requests and bulk-approve them</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>Toast: "3 requests approved." All 3 move to Approved. Attendance records updated for each</t>
-        </is>
-      </c>
-      <c r="E48" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Submit MC request</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Submit an MC request for a future weekday within the current cycle</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Toast: "Request submitted for approval." MC badge shown in amber. Admin inbox shows new request with amber badge</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr"/>
-      <c r="G48" s="13" t="inlineStr"/>
+      <c r="G48" s="10" t="inlineStr"/>
     </row>
     <row r="49" ht="27" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>3.11</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Admin - bulk reject leaves</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>Select multiple pending leave requests and bulk-reject with a reason</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>All selected requests rejected. Each record stores the same rejection reason. Toast confirms count</t>
-        </is>
-      </c>
-      <c r="E49" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>Submit Personal Leave request</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Submit a Personal Leave request for a future weekday within the current cycle</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>Toast: "Request submitted for approval." Personal Leave badge shown in red. Admin inbox shows new request with red badge</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F49" s="9" t="inlineStr"/>
-      <c r="G49" s="10" t="inlineStr"/>
-    </row>
-    <row r="50" ht="6" customHeight="1"/>
-    <row r="51" ht="13.5" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4. SIGNUP APPROVAL WORKFLOW</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="5" t="n"/>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="n"/>
-      <c r="G51" s="5" t="n"/>
+      <c r="G49" s="13" t="inlineStr"/>
+    </row>
+    <row r="50" ht="27" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Submit request - already pending</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Attempt to submit a second leave request while one is already pending</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Error: "You already have a pending request." No second request is created</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr"/>
+      <c r="G50" s="10" t="inlineStr"/>
+    </row>
+    <row r="51" ht="27" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Submit request - past date</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>Attempt to submit a leave request for a date before today</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>Error: "Cannot submit a request for a past date." No request is created</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr"/>
+      <c r="G51" s="13" t="inlineStr"/>
     </row>
     <row r="52" ht="27" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Approve new signup</t>
+          <t>Submit request - weekend</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Admin approves a pending signup for a brand-new user</t>
+          <t>Attempt to submit a leave request for a Saturday or Sunday</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Personnel record created and linked to the auth account. Person appears on the roster. Toast: "[Name] approved and added to the roster."</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Error shown: weekend dates are not valid for leave requests. No request created</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr"/>
@@ -1908,27 +1908,27 @@
     <row r="53" ht="27" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Approve returning reservist</t>
+          <t>Submit request - public holiday</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Admin approves a signup where the contact matches an inactive personnel record (returning reservist)</t>
+          <t>Attempt to submit a leave request for a Singapore public holiday</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Existing record is reactivated and assigned to the new cycle. Auth is linked. Person appears on roster labelled Returning</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Error shown: public holiday dates are not valid. No request created</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr"/>
@@ -1937,27 +1937,27 @@
     <row r="54" ht="27" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Approve - already on roster</t>
+          <t>Submit request - outside cycle</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Admin approves a signup where the contact already has an active personnel record</t>
+          <t>Attempt to submit a leave request for a date outside the reservist's batch start and end dates</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Auth account is linked to the existing record. No duplicate personnel entry is created</t>
-        </is>
-      </c>
-      <c r="E54" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
+          <t>Error: "The selected date is outside your current cycle."</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F54" s="9" t="inlineStr"/>
@@ -1966,22 +1966,22 @@
     <row r="55" ht="27" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Approve - personnel.add fails</t>
+          <t>Submit request - duplicate date</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Simulate a DB failure on personnel.add after the signup has been marked approved (requires mocking)</t>
+          <t>Submit a request for a date that already has a non-cancelled, non-rejected request</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Signup status is reverted to Pending. Error toast shown. Admin can retry. No orphaned approved record</t>
+          <t>Error: "You already submitted a request for this date." No duplicate is created</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -1995,22 +1995,22 @@
     <row r="56" ht="27" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Reject signup</t>
+          <t>Approved leave blocks check-in</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Admin rejects a pending signup request</t>
+          <t>Have an admin approve a leave request for today, then attempt to check in as that reservist</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Request moves to Rejected tab. Auth account is retained (so the person can re-apply). No personnel record is created</t>
+          <t>Check-in screen shows that leave is approved for today. Phase tiles are hidden or action is blocked</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -2024,27 +2024,27 @@
     <row r="57" ht="27" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>Reopen rejected signup</t>
+          <t>Cancel pending request</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Admin re-opens a previously rejected signup</t>
+          <t>Cancel a pending leave request before the admin has reviewed it</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Signup moves back to Pending tab. Admin can approve or reject again</t>
-        </is>
-      </c>
-      <c r="E57" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
+          <t>Toast: "Request cancelled." Status in history changes to Cancelled. DB record status is updated. Pending request badge clears</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F57" s="9" t="inlineStr"/>
@@ -2053,789 +2053,833 @@
     <row r="58" ht="27" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Bulk approve signups</t>
+          <t>Cancel already-reviewed request</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Select 3 pending signups and bulk-approve them</t>
+          <t>Attempt to cancel a request that an admin has already approved or rejected</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>All 3 approved. Each person added to the roster. Toast: "3 signups approved." Personnel list refreshes</t>
-        </is>
-      </c>
-      <c r="E58" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
+          <t>Error: "Request was already reviewed by an admin." History reloads to show the current status</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F58" s="9" t="inlineStr"/>
       <c r="G58" s="10" t="inlineStr"/>
     </row>
-    <row r="59" ht="6" customHeight="1"/>
-    <row r="60" ht="13.5" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5. ADMIN - ROSTER AND ATTENDANCE MANAGEMENT</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="n"/>
-      <c r="C60" s="5" t="n"/>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="n"/>
-      <c r="G60" s="5" t="n"/>
+    <row r="59" ht="27" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>Admin approve MC leave</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>Admin approves an MC leave request from the Requests inbox</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Request moves to Approved. Attendance record for that date is updated to MC. If the date is today, the roster updates immediately</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr"/>
+      <c r="G59" s="13" t="inlineStr"/>
+    </row>
+    <row r="60" ht="27" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Admin reject leave with reason</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Admin rejects a leave request and provides a written reason</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Request moves to Rejected. Rejection reason is recorded. Reservist sees the rejection reason in their history</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr"/>
+      <c r="G60" s="10" t="inlineStr"/>
     </row>
     <row r="61" ht="27" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>Admin bulk approve leaves</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>Select 3 pending leave requests and bulk-approve them</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>Toast: "3 requests approved." All 3 move to Approved. Attendance records updated for each</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr"/>
+      <c r="G61" s="13" t="inlineStr"/>
+    </row>
+    <row r="62" ht="27" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Admin bulk reject leaves</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Select multiple pending leave requests and bulk-reject with a reason</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>All selected requests rejected. Each record stores the same rejection reason. Toast confirms count</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr"/>
+      <c r="G62" s="10" t="inlineStr"/>
+    </row>
+    <row r="63" ht="27" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>Void leave on mark present</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>Admin marks a reservist with an approved leave as Present via the roster or log</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>Approved leave is voided in DB. approvedLeavesCache for that person/date is cleared. Reservist can submit a new request for that date</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr"/>
+      <c r="G63" s="13" t="inlineStr"/>
+    </row>
+    <row r="64" ht="27" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Re-submit after void</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>After admin has voided a reservist's approved leave by marking them present, reservist submits a new request for the same date</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>New request created without duplicate error. Appears in admin inbox as pending</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr"/>
+      <c r="G64" s="10" t="inlineStr"/>
+    </row>
+    <row r="65" ht="27" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>4.18</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>Request deduplication in history</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>Reservist has an approved request and a later withdrawn request for the same date</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>Only one entry is shown in the request history for that date. The approved entry takes priority over the withdrawn one</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr"/>
+      <c r="G65" s="13" t="inlineStr"/>
+    </row>
+    <row r="66" ht="27" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>History type badges</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>View the request history in the Info tab after submitting both an MC and a Personal Leave request</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>MC entries show an amber badge. Personal Leave entries show a red badge. Status badges (Submitted, Approved, Declined, Withdrawn) are correct</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr"/>
+      <c r="G66" s="10" t="inlineStr"/>
+    </row>
+    <row r="67" ht="27" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>Declined request shows reason</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>Admin rejects a request with a written reason; reservist then views their request history</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>The declined request row shows the supervisor's written reason inline in the history view</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr"/>
+      <c r="G67" s="13" t="inlineStr"/>
+    </row>
+    <row r="68" ht="6" customHeight="1"/>
+    <row r="69" ht="13.5" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. SIGNUP APPROVAL WORKFLOW</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n"/>
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="5" t="n"/>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="n"/>
+      <c r="G69" s="5" t="n"/>
+    </row>
+    <row r="70" ht="27" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Manual status override - present</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>Admin manually marks a reservist as Present on today's roster</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Status updates immediately. DB record is upserted. Toast: "Marked present"</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F61" s="9" t="inlineStr"/>
-      <c r="G61" s="10" t="inlineStr"/>
-    </row>
-    <row r="62" ht="27" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Approve new signup</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>Admin approves a pending signup for a brand-new user</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Personnel record created and linked to the auth account. Person appears on the roster. Toast: "[Name] approved and added to the roster."</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr"/>
+      <c r="G70" s="10" t="inlineStr"/>
+    </row>
+    <row r="71" ht="27" customHeight="1">
+      <c r="A71" s="11" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B62" s="12" t="inlineStr">
-        <is>
-          <t>Manual status override - past</t>
-        </is>
-      </c>
-      <c r="C62" s="12" t="inlineStr">
-        <is>
-          <t>Navigate to a past date (viewOffset negative) and manually override a status</t>
-        </is>
-      </c>
-      <c r="D62" s="12" t="inlineStr">
-        <is>
-          <t>Status updates in attendanceCache for that date. DB record updated. Does not affect today's attendance</t>
-        </is>
-      </c>
-      <c r="E62" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F62" s="9" t="inlineStr"/>
-      <c r="G62" s="13" t="inlineStr"/>
-    </row>
-    <row r="63" ht="27" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>Approve returning reservist</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>Admin approves a signup where the contact matches an inactive personnel record (returning reservist)</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>Existing record is reactivated and assigned to the new cycle. Auth is linked. Person appears on roster labelled Returning</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr"/>
+      <c r="G71" s="13" t="inlineStr"/>
+    </row>
+    <row r="72" ht="27" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Mark all absent</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>Use "Mark All Absent" on a day where some reservists have no status</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Only reservists with no status or "pending" status are marked absent. Those already marked Present, MC, or Absent are unaffected</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F63" s="9" t="inlineStr"/>
-      <c r="G63" s="10" t="inlineStr"/>
-    </row>
-    <row r="64" ht="27" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Approve - already on roster</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>Admin approves a signup where the contact already has an active personnel record</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Auth account is linked to the existing record. No duplicate personnel entry is created</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr"/>
+      <c r="G72" s="10" t="inlineStr"/>
+    </row>
+    <row r="73" ht="27" customHeight="1">
+      <c r="A73" s="11" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
-        <is>
-          <t>Mark all absent - future blocked</t>
-        </is>
-      </c>
-      <c r="C64" s="12" t="inlineStr">
-        <is>
-          <t>Navigate to a future date (viewOffset positive) and attempt "Mark All Absent"</t>
-        </is>
-      </c>
-      <c r="D64" s="12" t="inlineStr">
-        <is>
-          <t>Action is blocked. No status changes. Confirm dialog closes immediately</t>
-        </is>
-      </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F64" s="9" t="inlineStr"/>
-      <c r="G64" s="13" t="inlineStr"/>
-    </row>
-    <row r="65" ht="27" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>Approve - personnel.add fails</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>Simulate a DB failure on personnel.add after the signup has been marked approved (requires mocking)</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>Signup status is reverted to Pending. Error toast shown. Admin can retry. No orphaned approved record</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr"/>
+      <c r="G73" s="13" t="inlineStr"/>
+    </row>
+    <row r="74" ht="27" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>Mark all present</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>Use "Mark All Present" on today's roster</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>All reservists with no status are marked Present with current time as check-in. Those already marked are unaffected</t>
-        </is>
-      </c>
-      <c r="E65" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F65" s="9" t="inlineStr"/>
-      <c r="G65" s="10" t="inlineStr"/>
-    </row>
-    <row r="66" ht="27" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Reject signup</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>Admin rejects a pending signup request</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Request moves to Rejected tab. Auth account is retained (so the person can re-apply). No personnel record is created</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr"/>
+      <c r="G74" s="10" t="inlineStr"/>
+    </row>
+    <row r="75" ht="27" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
-        <is>
-          <t>Manual time correction</t>
-        </is>
-      </c>
-      <c r="C66" s="12" t="inlineStr">
-        <is>
-          <t>Edit a reservist's times for all 4 phases from the Log tab</t>
-        </is>
-      </c>
-      <c r="D66" s="12" t="inlineStr">
-        <is>
-          <t>Times saved. Record flagged as GPS bypassed. Edit log entry created with editor name and timestamp</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F66" s="9" t="inlineStr"/>
-      <c r="G66" s="13" t="inlineStr"/>
-    </row>
-    <row r="67" ht="27" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>Reopen rejected signup</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>Admin re-opens a previously rejected signup</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>Signup moves back to Pending tab. Admin can approve or reject again</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr"/>
+      <c r="G75" s="13" t="inlineStr"/>
+    </row>
+    <row r="76" ht="27" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>Time correction - invalid order</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>Enter a Phase 2 time that is earlier than Phase 1</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>Error toast: "Lunch out must be after Check-in." Save is blocked. Offending field is highlighted</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F67" s="9" t="inlineStr"/>
-      <c r="G67" s="10" t="inlineStr"/>
-    </row>
-    <row r="68" ht="27" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Bulk approve signups</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>Select 3 pending signups and bulk-approve them</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>All 3 approved. Each person added to the roster. Toast: "3 signups approved." Personnel list refreshes</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr"/>
+      <c r="G76" s="10" t="inlineStr"/>
+    </row>
+    <row r="77" ht="27" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
-        <is>
-          <t>Time correction - missing prereq</t>
-        </is>
-      </c>
-      <c r="C68" s="12" t="inlineStr">
-        <is>
-          <t>Enter a Phase 4 time without providing Phase 3</t>
-        </is>
-      </c>
-      <c r="D68" s="12" t="inlineStr">
-        <is>
-          <t>Error: "Return from lunch time is required when recording checkout." Save is blocked</t>
-        </is>
-      </c>
-      <c r="E68" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F68" s="9" t="inlineStr"/>
-      <c r="G68" s="13" t="inlineStr"/>
-    </row>
-    <row r="69" ht="27" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>5.9</t>
-        </is>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>Non-reporting day toggle</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>Toggle a weekday as a no-reporting day from the Roster tab</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>Day is added to the no_report_days table. Calendar, attendance rate calculations, and exports exclude this day</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F69" s="9" t="inlineStr"/>
-      <c r="G69" s="10" t="inlineStr"/>
-    </row>
-    <row r="70" ht="27" customHeight="1">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t>5.10</t>
-        </is>
-      </c>
-      <c r="B70" s="12" t="inlineStr">
-        <is>
-          <t>Auto-absent on date change</t>
-        </is>
-      </c>
-      <c r="C70" s="12" t="inlineStr">
-        <is>
-          <t>Leave the admin app open past midnight on a reporting day with some reservists unchecked</t>
-        </is>
-      </c>
-      <c r="D70" s="12" t="inlineStr">
-        <is>
-          <t>At midnight, unchecked reservists (excluding those with approved leaves or pending leave requests) are automatically marked absent for the previous day</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr"/>
-      <c r="G70" s="13" t="inlineStr"/>
-    </row>
-    <row r="71" ht="27" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>5.11</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Roster search</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>Search for a person by partial name in the roster search bar</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>List filters in real time. Clear button resets the search</t>
-        </is>
-      </c>
-      <c r="E71" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="inlineStr"/>
-      <c r="G71" s="10" t="inlineStr"/>
-    </row>
-    <row r="72" ht="27" customHeight="1">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t>5.12</t>
-        </is>
-      </c>
-      <c r="B72" s="12" t="inlineStr">
-        <is>
-          <t>Log status filter</t>
-        </is>
-      </c>
-      <c r="C72" s="12" t="inlineStr">
-        <is>
-          <t>Filter the daily log by "Present", "MC", and "Absent" status buttons</t>
-        </is>
-      </c>
-      <c r="D72" s="12" t="inlineStr">
-        <is>
-          <t>"All" resets to unfiltered view. Log shows only matching records for the selected filter</t>
-        </is>
-      </c>
-      <c r="E72" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F72" s="9" t="inlineStr"/>
-      <c r="G72" s="13" t="inlineStr"/>
-    </row>
-    <row r="73" ht="27" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>5.13</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>Day navigation and cross-cycle</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>Use previous/next day arrows to navigate from one cycle's last day to the next cycle's first day</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Active cycle switches automatically. Attendance data loads for the new date. Batch label updates in header</t>
-        </is>
-      </c>
-      <c r="E73" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F73" s="9" t="inlineStr"/>
-      <c r="G73" s="10" t="inlineStr"/>
-    </row>
-    <row r="74" ht="27" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t>5.14</t>
-        </is>
-      </c>
-      <c r="B74" s="12" t="inlineStr">
-        <is>
-          <t>Welfare note</t>
-        </is>
-      </c>
-      <c r="C74" s="12" t="inlineStr">
-        <is>
-          <t>Admin writes a welfare note for a specific person on a specific date</t>
-        </is>
-      </c>
-      <c r="D74" s="12" t="inlineStr">
-        <is>
-          <t>Note is saved to the attendance record. Visible in both the roster and the log view. Toast: "Note saved."</t>
-        </is>
-      </c>
-      <c r="E74" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F74" s="9" t="inlineStr"/>
-      <c r="G74" s="13" t="inlineStr"/>
-    </row>
-    <row r="75" ht="27" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>5.15</t>
-        </is>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>Real-time roster update</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>Have a reservist check in while the admin has the overview or log tab open</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Admin's roster updates in real time without a page refresh. The realtime status indicator is green</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="inlineStr"/>
-      <c r="G75" s="10" t="inlineStr"/>
-    </row>
-    <row r="76" ht="6" customHeight="1"/>
-    <row r="77" ht="13.5" customHeight="1">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6. PERSONNEL MANAGEMENT</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="n"/>
-      <c r="C77" s="5" t="n"/>
-      <c r="D77" s="5" t="n"/>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="n"/>
-      <c r="G77" s="5" t="n"/>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>Signup search and filter</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>Use the collapsible search bar and filter pills (All, New, Returning) in the signups panel</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>Results update correctly. Red dot appears on the search icon when a filter is active. Clear resets all filters</t>
+        </is>
+      </c>
+      <c r="E77" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr"/>
+      <c r="G77" s="13" t="inlineStr"/>
     </row>
     <row r="78" ht="27" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Add new person</t>
+          <t>Select-all checkbox</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>Admin adds a new person via the People tab with a valid name, SG contact, and password</t>
+          <t>Tick the select-all checkbox in the signups header with search active</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Auth account and personnel record created. Person appears on the roster immediately. Toast: "[Name] added to roster."</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Only visible (filtered) signups are selected. Unchecking deselects all. Count badge updates correctly</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr"/>
       <c r="G78" s="10" t="inlineStr"/>
     </row>
-    <row r="79" ht="27" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
+    <row r="79" ht="6" customHeight="1"/>
+    <row r="80" ht="13.5" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. ADMIN - ROSTER AND ATTENDANCE MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n"/>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="5" t="n"/>
+    </row>
+    <row r="81" ht="27" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Manual status override - present</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Admin manually marks a reservist as Present on today's roster</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Status updates immediately. DB record is upserted. Toast: "Marked present"</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr"/>
+      <c r="G81" s="10" t="inlineStr"/>
+    </row>
+    <row r="82" ht="27" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
-        <is>
-          <t>Add person - auth fails, no orphan</t>
-        </is>
-      </c>
-      <c r="C79" s="12" t="inlineStr">
-        <is>
-          <t>Simulate a DB failure on personnel.add after auth.createUser succeeds (requires mocking)</t>
-        </is>
-      </c>
-      <c r="D79" s="12" t="inlineStr">
-        <is>
-          <t>Auth account is deleted automatically. Error toast shown. No orphaned auth account remains</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F79" s="9" t="inlineStr"/>
-      <c r="G79" s="13" t="inlineStr"/>
-    </row>
-    <row r="80" ht="27" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>Manual status override - past</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>Navigate to a past date (viewOffset negative) and manually override a status</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>Status updates in attendanceCache for that date. DB record updated. Does not affect today's attendance</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr"/>
+      <c r="G82" s="13" t="inlineStr"/>
+    </row>
+    <row r="83" ht="27" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>Add person - duplicate contact</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>Attempt to add a person with a contact number already on the current roster</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>Error: "This contact is already on the roster." No account or record is created</t>
-        </is>
-      </c>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F80" s="9" t="inlineStr"/>
-      <c r="G80" s="10" t="inlineStr"/>
-    </row>
-    <row r="81" ht="27" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Mark all absent</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Use "Mark All Absent" on a day where some reservists have no status</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Only reservists with no status or "pending" status are marked absent. Those already marked Present, MC, or Absent are unaffected</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr"/>
+      <c r="G83" s="10" t="inlineStr"/>
+    </row>
+    <row r="84" ht="27" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
-        <is>
-          <t>Add person - returning detected</t>
-        </is>
-      </c>
-      <c r="C81" s="12" t="inlineStr">
-        <is>
-          <t>Add a person whose contact matches an existing inactive record</t>
-        </is>
-      </c>
-      <c r="D81" s="12" t="inlineStr">
-        <is>
-          <t>Re-enrollment prompt appears. Confirming reactivates the old record and assigns it to the current cycle. No new account created</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F81" s="9" t="inlineStr"/>
-      <c r="G81" s="13" t="inlineStr"/>
-    </row>
-    <row r="82" ht="27" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>Mark all absent - future blocked</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>Navigate to a future date (viewOffset positive) and attempt "Mark All Absent"</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>Action is blocked. No status changes. Confirm dialog closes immediately</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr"/>
+      <c r="G84" s="13" t="inlineStr"/>
+    </row>
+    <row r="85" ht="27" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Deactivate person</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>Admin removes a reservist from the roster using the deactivate option</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>Person is removed from the active roster. is_active set to false in DB. Historical attendance records are preserved</t>
-        </is>
-      </c>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F82" s="9" t="inlineStr"/>
-      <c r="G82" s="10" t="inlineStr"/>
-    </row>
-    <row r="83" ht="27" customHeight="1">
-      <c r="A83" s="11" t="inlineStr">
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Mark all present</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Use "Mark All Present" on today's roster</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>All reservists with no status are marked Present with current time as check-in. Those already marked are unaffected</t>
+        </is>
+      </c>
+      <c r="E85" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F85" s="9" t="inlineStr"/>
+      <c r="G85" s="10" t="inlineStr"/>
+    </row>
+    <row r="86" ht="27" customHeight="1">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
       </c>
-      <c r="B83" s="12" t="inlineStr">
-        <is>
-          <t>Password reset</t>
-        </is>
-      </c>
-      <c r="C83" s="12" t="inlineStr">
-        <is>
-          <t>Admin resets a reservist's password from the roster</t>
-        </is>
-      </c>
-      <c r="D83" s="12" t="inlineStr">
-        <is>
-          <t>Toast: "[Name]'s password has been reset." Reservist can now log in with the new password</t>
-        </is>
-      </c>
-      <c r="E83" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F83" s="9" t="inlineStr"/>
-      <c r="G83" s="13" t="inlineStr"/>
-    </row>
-    <row r="84" ht="27" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>Manual time correction</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>Edit a reservist's times for all 4 phases from the Log tab</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>Times saved. Record flagged as GPS bypassed. Edit log entry created with editor name and timestamp</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr"/>
+      <c r="G86" s="13" t="inlineStr"/>
+    </row>
+    <row r="87" ht="27" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Bulk add personnel</t>
-        </is>
-      </c>
-      <c r="C84" s="7" t="inlineStr">
-        <is>
-          <t>Paste a list of "Name, Contact" pairs and confirm bulk add</t>
-        </is>
-      </c>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>Valid entries are added. Invalid lines are skipped. Existing contacts are skipped. Toast summarises added/skipped/failed counts</t>
-        </is>
-      </c>
-      <c r="E84" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr"/>
-      <c r="G84" s="10" t="inlineStr"/>
-    </row>
-    <row r="85" ht="27" customHeight="1">
-      <c r="A85" s="11" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>Time correction - invalid order</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>Enter a Phase 2 time that is earlier than Phase 1</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Error toast: "Lunch out must be after Check-in." Save is blocked. Offending field is highlighted</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr"/>
+      <c r="G87" s="10" t="inlineStr"/>
+    </row>
+    <row r="88" ht="27" customHeight="1">
+      <c r="A88" s="11" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
       </c>
-      <c r="B85" s="12" t="inlineStr">
-        <is>
-          <t>Person attendance history</t>
-        </is>
-      </c>
-      <c r="C85" s="12" t="inlineStr">
-        <is>
-          <t>Open the attendance history modal for a specific person</t>
-        </is>
-      </c>
-      <c r="D85" s="12" t="inlineStr">
-        <is>
-          <t>Full history loads with dates, statuses, check-in times, and any admin corrections flagged</t>
-        </is>
-      </c>
-      <c r="E85" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F85" s="9" t="inlineStr"/>
-      <c r="G85" s="13" t="inlineStr"/>
-    </row>
-    <row r="86" ht="27" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>6.9</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>Member search - cross-cycle</t>
-        </is>
-      </c>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>Search for a person who exists in a previous cycle (not the current one)</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>Person appears in results with their cycle and status shown. Can be permanently deleted from here</t>
-        </is>
-      </c>
-      <c r="E86" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F86" s="9" t="inlineStr"/>
-      <c r="G86" s="10" t="inlineStr"/>
-    </row>
-    <row r="87" ht="6" customHeight="1"/>
-    <row r="88" ht="13.5" customHeight="1">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7. SUPER ADMIN (MASTER)</t>
-        </is>
-      </c>
-      <c r="B88" s="5" t="n"/>
-      <c r="C88" s="5" t="n"/>
-      <c r="D88" s="5" t="n"/>
-      <c r="E88" s="5" t="n"/>
-      <c r="F88" s="5" t="n"/>
-      <c r="G88" s="5" t="n"/>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>Time correction - missing prereq</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>Enter a Phase 4 time without providing Phase 3</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>Error: "Return from lunch time is required when recording checkout." Save is blocked</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr"/>
+      <c r="G88" s="13" t="inlineStr"/>
     </row>
     <row r="89" ht="27" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>Add admin account</t>
+          <t>Non-reporting day toggle</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Logged in as Master, add a new admin with a valid name, contact, and password</t>
+          <t>Toggle a weekday as a no-reporting day from the Roster tab</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Auth account and personnel record (role=admin) created. Appears in admins list. Toast: "[Name] added as admin."</t>
+          <t>Day is added to the no_report_days table. Calendar, attendance rate calculations, and exports exclude this day</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -2849,22 +2893,22 @@
     <row r="90" ht="27" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t>Add admin - auth fails, no orphan</t>
+          <t>Auto-absent on date change</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>Simulate DB failure on personnel.add after auth.createUser succeeds (requires mocking)</t>
+          <t>Leave the admin app open past midnight on a reporting day with some reservists unchecked</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>Auth account is deleted automatically. Error toast shown. No orphaned auth account</t>
+          <t>At midnight, unchecked reservists (excluding those with approved leaves or pending leave requests) are automatically marked absent for the previous day</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
@@ -2878,27 +2922,27 @@
     <row r="91" ht="27" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>Add admin - access denied</t>
+          <t>Roster search</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Call addAdmin handler while logged in as a regular admin (not Master)</t>
+          <t>Search for a person by partial name in the roster search bar</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Error: "Access denied." No account created. Handler returns early even if UI bypass is attempted</t>
-        </is>
-      </c>
-      <c r="E91" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>List filters in real time. Clear button resets the search</t>
+        </is>
+      </c>
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr"/>
@@ -2907,27 +2951,27 @@
     <row r="92" ht="27" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t>Promote reservist to admin</t>
+          <t>Log status filter</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>Logged in as Master, promote an existing reservist to admin</t>
+          <t>Filter the daily log by "Present", "MC", and "Absent" status buttons</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>Person's role changes to admin. They disappear from the reservist list and appear in the admins list. Toast: "[Name] promoted to admin."</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>"All" resets to unfiltered view. Log shows only matching records for the selected filter</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr"/>
@@ -2936,27 +2980,27 @@
     <row r="93" ht="27" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>Demote admin to reservist</t>
+          <t>Day navigation and cross-cycle</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Logged in as Master, remove an admin's supervisor status</t>
+          <t>Use previous/next day arrows to navigate from one cycle's last day to the next cycle's first day</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Admin is removed from the admins list and returned to the reservist pool with no batch assignment. Toast confirms</t>
-        </is>
-      </c>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Active cycle switches automatically. Attendance data loads for the new date. Batch label updates in header</t>
+        </is>
+      </c>
+      <c r="E93" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr"/>
@@ -2965,70 +3009,114 @@
     <row r="94" ht="27" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t>Promote/demote - non-master</t>
+          <t>Welfare note</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>Call confirmPromoteAdmin or confirmDeactivateAdmin while logged in as a regular admin</t>
+          <t>Admin writes a welfare note for a specific person on a specific date</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>Error: "Access denied." No role change occurs</t>
-        </is>
-      </c>
-      <c r="E94" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Note is saved to the attendance record. Visible in both the roster and the log view. Toast: "Note saved."</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr"/>
       <c r="G94" s="13" t="inlineStr"/>
     </row>
-    <row r="95" ht="6" customHeight="1"/>
-    <row r="96" ht="13.5" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8. CYCLE MANAGEMENT</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="n"/>
-      <c r="C96" s="5" t="n"/>
-      <c r="D96" s="5" t="n"/>
-      <c r="E96" s="5" t="n"/>
-      <c r="F96" s="5" t="n"/>
-      <c r="G96" s="5" t="n"/>
+    <row r="95" ht="27" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>6.15</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Real-time roster update</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Have a reservist check in while the admin has the overview or log tab open</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Admin's roster updates in real time without a page refresh. The realtime status indicator is green</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr"/>
+      <c r="G95" s="10" t="inlineStr"/>
+    </row>
+    <row r="96" ht="27" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>6.16</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>Low attendance indicator</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>View a reservist whose attendance rate is below 75% in the roster or log</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>Amber attendance percentage and short indicator text appear inline next to the contact number. No separate row or pill is added</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr"/>
+      <c r="G96" s="13" t="inlineStr"/>
     </row>
     <row r="97" ht="27" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>Create cycle</t>
+          <t>Late badge with reason</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Admin creates a new cycle by selecting a start date</t>
+          <t>View the log entry for a reservist who checked in more than 1 hour late with a written reason</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Cycle created with correct label (Cycle N/YYYY), start date (Tuesday), end date (14 days later, Monday), and dekit date (Wednesday). Appears in cycle list</t>
-        </is>
-      </c>
-      <c r="E97" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>A late badge appears inline on the log card showing the written reason (e.g. "Late · Dental appointment"). No expansion needed to read it</t>
+        </is>
+      </c>
+      <c r="E97" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr"/>
@@ -3037,22 +3125,22 @@
     <row r="98" ht="27" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t>Auto cycle creation on login</t>
+          <t>Late badge - no reason given</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>Admin logs in when fewer than 8 future cycles exist</t>
+          <t>View the log entry for a reservist who was forced through the late reason modal but submitted no reason</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>System automatically creates future cycles to bring the count to 8. No manual action required</t>
+          <t>Late badge shows "Late · No reason" inline on the log card</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
@@ -3066,27 +3154,27 @@
     <row r="99" ht="27" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>Rename cycle</t>
+          <t>Missing clock-out display</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Edit the label of an existing cycle</t>
+          <t>View a log entry where a reservist is marked Present but has no Phase 4 (end of shift) time</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Label updates in the header, cycle picker, and all references. DB record updated</t>
-        </is>
-      </c>
-      <c r="E99" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>The OUT column of the log card shows a dash on an orange background. No separate badge row is added below the card</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr"/>
@@ -3095,152 +3183,152 @@
     <row r="100" ht="27" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t>Meal allowance toggle</t>
+          <t>Mark present voids leave</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>Toggle meal allowance on for the current cycle</t>
+          <t>Admin marks a reservist with an approved leave as Present via the roster status button</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>Meal timer appears on reservist check-in screen. Meal eligibility badge appears in the admin log after 8h work. Toast: "Meal allowance forms activated."</t>
-        </is>
-      </c>
-      <c r="E100" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
+          <t>Approved leave is voided in the DB. The approvedLeavesCache entry for that person and date is removed immediately. Roster shows Present status</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr"/>
       <c r="G100" s="13" t="inlineStr"/>
     </row>
-    <row r="101" ht="27" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>Cycle notice (broadcast)</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>Post a notice for the current cycle</t>
-        </is>
-      </c>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>Notice appears as a banner on every reservist's check-in screen. Toast: "Notice posted to all reservists."</t>
-        </is>
-      </c>
-      <c r="E101" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F101" s="9" t="inlineStr"/>
-      <c r="G101" s="10" t="inlineStr"/>
-    </row>
-    <row r="102" ht="27" customHeight="1">
-      <c r="A102" s="11" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
-      </c>
-      <c r="B102" s="12" t="inlineStr">
-        <is>
-          <t>Bulk no-report days</t>
-        </is>
-      </c>
-      <c r="C102" s="12" t="inlineStr">
-        <is>
-          <t>Paste multiple dates in dd/mm/yyyy format and apply them as no-report days</t>
-        </is>
-      </c>
-      <c r="D102" s="12" t="inlineStr">
-        <is>
-          <t>Valid dates within the cycle are added. Dates outside the cycle range are ignored. Toast reports count added</t>
-        </is>
-      </c>
-      <c r="E102" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F102" s="9" t="inlineStr"/>
-      <c r="G102" s="13" t="inlineStr"/>
+    <row r="101" ht="6" customHeight="1"/>
+    <row r="102" ht="13.5" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. PERSONNEL MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n"/>
+      <c r="C102" s="5" t="n"/>
+      <c r="D102" s="5" t="n"/>
+      <c r="E102" s="5" t="n"/>
+      <c r="F102" s="5" t="n"/>
+      <c r="G102" s="5" t="n"/>
     </row>
     <row r="103" ht="27" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>Jump to date</t>
+          <t>Add new person</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Use the date jump field to navigate to a specific date in a different cycle</t>
+          <t>Admin adds a new person via the People tab with a valid name, SG contact, and password</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Active cycle switches to the one containing that date. View offset is set correctly. Attendance for that date loads</t>
-        </is>
-      </c>
-      <c r="E103" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
+          <t>Auth account and personnel record created. Person appears on the roster immediately. Toast: "[Name] added to roster."</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr"/>
       <c r="G103" s="10" t="inlineStr"/>
     </row>
-    <row r="104" ht="6" customHeight="1"/>
-    <row r="105" ht="13.5" customHeight="1">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  9. EXPORT AND REPORTS</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="n"/>
-      <c r="C105" s="5" t="n"/>
-      <c r="D105" s="5" t="n"/>
-      <c r="E105" s="5" t="n"/>
-      <c r="F105" s="5" t="n"/>
-      <c r="G105" s="5" t="n"/>
+    <row r="104" ht="27" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>Add person - auth fails, no orphan</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>Simulate a DB failure on personnel.add after auth.createUser succeeds (requires mocking)</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>Auth account is deleted automatically. Error toast shown. No orphaned auth account remains</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr"/>
+      <c r="G104" s="13" t="inlineStr"/>
+    </row>
+    <row r="105" ht="27" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Add person - duplicate contact</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>Attempt to add a person with a contact number already on the current roster</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Error: "This contact is already on the roster." No account or record is created</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr"/>
+      <c r="G105" s="10" t="inlineStr"/>
     </row>
     <row r="106" ht="27" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>Export XLS - data integrity</t>
-        </is>
-      </c>
-      <c r="C106" s="7" t="inlineStr">
-        <is>
-          <t>Export attendance for a cycle with known data and open in Excel</t>
-        </is>
-      </c>
-      <c r="D106" s="7" t="inlineStr">
-        <is>
-          <t>All dates, names, statuses (P/MC/A), totals, and rate percentages are correct. No-report days and public holidays are excluded. Admin-corrected records show P*</t>
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>Add person - returning detected</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>Add a person whose contact matches an existing inactive record</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>Re-enrollment prompt appears. Confirming reactivates the old record and assigns it to the current cycle. No new account created</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -3249,56 +3337,56 @@
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr"/>
-      <c r="G106" s="10" t="inlineStr"/>
+      <c r="G106" s="13" t="inlineStr"/>
     </row>
     <row r="107" ht="27" customHeight="1">
-      <c r="A107" s="11" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="B107" s="12" t="inlineStr">
-        <is>
-          <t>Export XLS - empty cycle</t>
-        </is>
-      </c>
-      <c r="C107" s="12" t="inlineStr">
-        <is>
-          <t>Attempt to export a cycle with no reservists</t>
-        </is>
-      </c>
-      <c r="D107" s="12" t="inlineStr">
-        <is>
-          <t>Error toast: "No reservists found in this cycle." No file is downloaded</t>
-        </is>
-      </c>
-      <c r="E107" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Deactivate person</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>Admin removes a reservist from the roster using the deactivate option</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>Person is removed from the active roster. is_active set to false in DB. Historical attendance records are preserved</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr"/>
-      <c r="G107" s="13" t="inlineStr"/>
+      <c r="G107" s="10" t="inlineStr"/>
     </row>
     <row r="108" ht="27" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>Print report preview</t>
-        </is>
-      </c>
-      <c r="C108" s="7" t="inlineStr">
-        <is>
-          <t>Open the Print/PDF report for a cycle with attendance data</t>
-        </is>
-      </c>
-      <c r="D108" s="7" t="inlineStr">
-        <is>
-          <t>Modal opens with formatted report showing all personnel, dates, status codes, summary stats. Print button opens browser print dialog</t>
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>Password reset</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>Admin resets a reservist's password from the roster</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>Toast: "[Name]'s password has been reset." Reservist can now log in with the new password</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
@@ -3307,27 +3395,27 @@
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr"/>
-      <c r="G108" s="10" t="inlineStr"/>
+      <c r="G108" s="13" t="inlineStr"/>
     </row>
     <row r="109" ht="27" customHeight="1">
-      <c r="A109" s="11" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
-      <c r="B109" s="12" t="inlineStr">
-        <is>
-          <t>Person history export</t>
-        </is>
-      </c>
-      <c r="C109" s="12" t="inlineStr">
-        <is>
-          <t>Open a person's history and export it to XLS</t>
-        </is>
-      </c>
-      <c r="D109" s="12" t="inlineStr">
-        <is>
-          <t>File downloads with name, date, status, in time, out time, and admin-correction flag for each row</t>
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>Bulk add personnel</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>Paste a list of "Name, Contact" pairs and confirm bulk add</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>Valid entries are added. Invalid lines are skipped. Existing contacts are skipped. Toast summarises added/skipped/failed counts</t>
         </is>
       </c>
       <c r="E109" s="14" t="inlineStr">
@@ -3336,70 +3424,114 @@
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr"/>
-      <c r="G109" s="13" t="inlineStr"/>
+      <c r="G109" s="10" t="inlineStr"/>
     </row>
     <row r="110" ht="27" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="B110" s="7" t="inlineStr">
-        <is>
-          <t>WhatsApp share</t>
-        </is>
-      </c>
-      <c r="C110" s="7" t="inlineStr">
-        <is>
-          <t>Tap the WhatsApp share button from the overview tab</t>
-        </is>
-      </c>
-      <c r="D110" s="7" t="inlineStr">
-        <is>
-          <t>Pre-filled attendance summary opens in WhatsApp (or wa.me link). Message contains today's date, present/MC/absent counts, and list of names</t>
-        </is>
-      </c>
-      <c r="E110" s="15" t="inlineStr">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>Person attendance history</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>Open the attendance history modal for a specific person</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>Full history loads with dates, statuses, check-in times, and any admin corrections flagged</t>
+        </is>
+      </c>
+      <c r="E110" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr"/>
+      <c r="G110" s="13" t="inlineStr"/>
+    </row>
+    <row r="111" ht="27" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>Collapsible action bar</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>Tap the chevron on a personnel card to expand its action bar, then tap another card's chevron</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>Action bar expands on the tapped card. The previously expanded card collapses automatically. Only one card is expanded at a time</t>
+        </is>
+      </c>
+      <c r="E111" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr"/>
+      <c r="G111" s="10" t="inlineStr"/>
+    </row>
+    <row r="112" ht="27" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>7.10</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>Avatar lightbox</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>Tap any reservist's profile photo in the roster, overview, or log</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>Photo opens in an enlarged lightbox overlay. Tapping outside the photo closes the lightbox</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F110" s="9" t="inlineStr"/>
-      <c r="G110" s="10" t="inlineStr"/>
-    </row>
-    <row r="111" ht="6" customHeight="1"/>
-    <row r="112" ht="13.5" customHeight="1">
-      <c r="A112" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10. ACCOUNT MANAGEMENT</t>
-        </is>
-      </c>
-      <c r="B112" s="5" t="n"/>
-      <c r="C112" s="5" t="n"/>
-      <c r="D112" s="5" t="n"/>
-      <c r="E112" s="5" t="n"/>
-      <c r="F112" s="5" t="n"/>
-      <c r="G112" s="5" t="n"/>
+      <c r="F112" s="9" t="inlineStr"/>
+      <c r="G112" s="13" t="inlineStr"/>
     </row>
     <row r="113" ht="27" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>Change display name</t>
+          <t>Added by / Approved by label</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>Change the display name from account settings</t>
+          <t>View a personnel card for someone added directly by admin vs. someone who self-signed up</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Name updates in the header chip and in DB. Toast: "Display name updated."</t>
+          <t>"Added by [Name]" appears for direct adds. "Approved by [Name]" appears for self-signup approvals. Blank if neither applies</t>
         </is>
       </c>
       <c r="E113" s="15" t="inlineStr">
@@ -3413,27 +3545,27 @@
     <row r="114" ht="27" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Click row opens history</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>Change password with correct current password and a matching new password (min 6 chars)</t>
+          <t>In the Overview or Log tab, click/tap a person's name or row</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>Toast: "Password updated." New password works on next login. Old password no longer works</t>
-        </is>
-      </c>
-      <c r="E114" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>The person's attendance history modal opens directly. No need to navigate to the People tab first</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr"/>
@@ -3442,409 +3574,2004 @@
     <row r="115" ht="27" customHeight="1">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>Change password - wrong current</t>
+          <t>Member search - cross-cycle</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>Attempt to change password with an incorrect current password</t>
+          <t>Search for a person who exists in a previous cycle (not the current one)</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>Error: "Current password is incorrect." Password is not changed</t>
-        </is>
-      </c>
-      <c r="E115" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Person appears in results with their cycle and status shown. Can be permanently deleted from here</t>
+        </is>
+      </c>
+      <c r="E115" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr"/>
       <c r="G115" s="10" t="inlineStr"/>
     </row>
-    <row r="116" ht="27" customHeight="1">
-      <c r="A116" s="11" t="inlineStr">
+    <row r="116" ht="6" customHeight="1"/>
+    <row r="117" ht="13.5" customHeight="1">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. SUPER ADMIN (MASTER)</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n"/>
+      <c r="C117" s="5" t="n"/>
+      <c r="D117" s="5" t="n"/>
+      <c r="E117" s="5" t="n"/>
+      <c r="F117" s="5" t="n"/>
+      <c r="G117" s="5" t="n"/>
+    </row>
+    <row r="118" ht="27" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>Add admin account</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>Logged in as Master, add a new admin with a valid name, contact, and password</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>Auth account and personnel record (role=admin) created. Appears in admins list. Toast: "[Name] added as admin."</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="inlineStr"/>
+      <c r="G118" s="10" t="inlineStr"/>
+    </row>
+    <row r="119" ht="27" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>Add admin - auth fails, no orphan</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>Simulate DB failure on personnel.add after auth.createUser succeeds (requires mocking)</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>Auth account is deleted automatically. Error toast shown. No orphaned auth account</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="inlineStr"/>
+      <c r="G119" s="13" t="inlineStr"/>
+    </row>
+    <row r="120" ht="27" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>Add admin - access denied</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>Call addAdmin handler while logged in as a regular admin (not Master)</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>Error: "Access denied." No account created. Handler returns early even if UI bypass is attempted</t>
+        </is>
+      </c>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr"/>
+      <c r="G120" s="10" t="inlineStr"/>
+    </row>
+    <row r="121" ht="27" customHeight="1">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>Promote reservist to admin</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>Logged in as Master, promote an existing reservist to admin</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>Person's role changes to admin. They disappear from the reservist list and appear in the admins list. Toast: "[Name] promoted to admin."</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F121" s="9" t="inlineStr"/>
+      <c r="G121" s="13" t="inlineStr"/>
+    </row>
+    <row r="122" ht="27" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>Demote admin to reservist</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>Logged in as Master, remove an admin's supervisor status</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>Admin is removed from the admins list and returned to the reservist pool with no batch assignment. Toast confirms</t>
+        </is>
+      </c>
+      <c r="E122" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F122" s="9" t="inlineStr"/>
+      <c r="G122" s="10" t="inlineStr"/>
+    </row>
+    <row r="123" ht="27" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>Promote/demote - non-master</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>Call confirmPromoteAdmin or confirmDeactivateAdmin while logged in as a regular admin</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>Error: "Access denied." No role change occurs</t>
+        </is>
+      </c>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F123" s="9" t="inlineStr"/>
+      <c r="G123" s="13" t="inlineStr"/>
+    </row>
+    <row r="124" ht="27" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>Reset supervisor password</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>Logged in as Master, reset a supervisor's password from the Team tab</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>Password updated in DB. Supervisor can log in with new password. Toast confirms reset</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F124" s="9" t="inlineStr"/>
+      <c r="G124" s="10" t="inlineStr"/>
+    </row>
+    <row r="125" ht="27" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>Department switcher - reload</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>Use the department dropdown in the header to switch from Dept A to Dept B</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>All data reloads for Dept B: roster, batches, personnel, pending requests, leave requests. Dept A data is cleared</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F125" s="9" t="inlineStr"/>
+      <c r="G125" s="13" t="inlineStr"/>
+    </row>
+    <row r="126" ht="27" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>Department switcher - cycle restore</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>Switch from Dept A to Dept B, navigate to a cycle, then switch back to Dept A</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>The last-selected cycle for Dept A is restored when switching back. Each department remembers its own cycle context independently</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="inlineStr"/>
+      <c r="G126" s="10" t="inlineStr"/>
+    </row>
+    <row r="127" ht="27" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>8.10</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>Department switcher - state clear</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>Enter a search term or apply a filter in Dept A, then switch to Dept B</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>Search text and filter state are cleared on switch. No stale text from the previous department appears</t>
+        </is>
+      </c>
+      <c r="E127" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F127" s="9" t="inlineStr"/>
+      <c r="G127" s="13" t="inlineStr"/>
+    </row>
+    <row r="128" ht="27" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>8.11</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>Cross-dept signup isolation</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>Log in as Master in Dept A. Have a Dept B user submit a signup request</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>The Dept B signup does not appear in the Dept A Requests tab. Switching to Dept B shows the signup correctly</t>
+        </is>
+      </c>
+      <c r="E128" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F128" s="9" t="inlineStr"/>
+      <c r="G128" s="10" t="inlineStr"/>
+    </row>
+    <row r="129" ht="27" customHeight="1">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>8.12</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>Cross-dept leave isolation</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>Log in as Master in Dept A. Have a Dept B reservist submit a leave request</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>The Dept B leave request does not appear in the Dept A Requests tab</t>
+        </is>
+      </c>
+      <c r="E129" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F129" s="9" t="inlineStr"/>
+      <c r="G129" s="13" t="inlineStr"/>
+    </row>
+    <row r="130" ht="27" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>8.13</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>Cross-dept cycle notice isolation</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>Post a cycle notice in Dept A. Log in as a Dept B reservist</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>The Dept A notice banner does not appear on the Dept B reservist's check-in screen</t>
+        </is>
+      </c>
+      <c r="E130" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F130" s="9" t="inlineStr"/>
+      <c r="G130" s="10" t="inlineStr"/>
+    </row>
+    <row r="131" ht="27" customHeight="1">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>8.14</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>Cross-dept notification isolation</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>Enable browser notifications as Master in Dept A. Have a Dept B leave request arrive</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>No browser notification fires while the Master is viewing Dept A. Switch to Dept B to see the notification trigger</t>
+        </is>
+      </c>
+      <c r="E131" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F131" s="9" t="inlineStr"/>
+      <c r="G131" s="13" t="inlineStr"/>
+    </row>
+    <row r="132" ht="27" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>Access: reservist tab block</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>Log in as a reservist and attempt to navigate to the Overview, Roster, Log, or People tab</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>Admin tabs are not rendered for reservists. URL-based navigation attempts do not load admin views</t>
+        </is>
+      </c>
+      <c r="E132" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr"/>
+      <c r="G132" s="10" t="inlineStr"/>
+    </row>
+    <row r="133" ht="27" customHeight="1">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>8.16</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>Access: admin RLS - leave</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>Attempt to submit a leave request for a different personnel ID via the API (not through the UI)</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>Supabase RLS blocks the insert. Request is rejected. Only the authenticated user can create requests for their own personnel_id</t>
+        </is>
+      </c>
+      <c r="E133" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="inlineStr"/>
+      <c r="G133" s="13" t="inlineStr"/>
+    </row>
+    <row r="134" ht="27" customHeight="1">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>8.17</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t>Access: admin cannot promote</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>Log in as a regular admin and attempt to call the promote or add-admin handler</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>Error: "Access denied." No role change occurs regardless of UI state</t>
+        </is>
+      </c>
+      <c r="E134" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="inlineStr"/>
+      <c r="G134" s="10" t="inlineStr"/>
+    </row>
+    <row r="135" ht="6" customHeight="1"/>
+    <row r="136" ht="13.5" customHeight="1">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9. CYCLE MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="n"/>
+      <c r="C136" s="5" t="n"/>
+      <c r="D136" s="5" t="n"/>
+      <c r="E136" s="5" t="n"/>
+      <c r="F136" s="5" t="n"/>
+      <c r="G136" s="5" t="n"/>
+    </row>
+    <row r="137" ht="27" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>Create cycle</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>Admin creates a new cycle by selecting a start date</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>Cycle created with correct label (Cycle N/YYYY), start date (Tuesday), end date (14 days later, Monday), and dekit date (Wednesday). Appears in cycle list</t>
+        </is>
+      </c>
+      <c r="E137" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="inlineStr"/>
+      <c r="G137" s="10" t="inlineStr"/>
+    </row>
+    <row r="138" ht="27" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="B138" s="12" t="inlineStr">
+        <is>
+          <t>Auto cycle creation on login</t>
+        </is>
+      </c>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>Admin logs in when fewer than 8 future cycles exist</t>
+        </is>
+      </c>
+      <c r="D138" s="12" t="inlineStr">
+        <is>
+          <t>System automatically creates future cycles to bring the count to 8. No manual action required</t>
+        </is>
+      </c>
+      <c r="E138" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="inlineStr"/>
+      <c r="G138" s="13" t="inlineStr"/>
+    </row>
+    <row r="139" ht="27" customHeight="1">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>Rename cycle</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>Edit the label of an existing cycle</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>Label updates in the header, cycle picker, and all references. DB record updated</t>
+        </is>
+      </c>
+      <c r="E139" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F139" s="9" t="inlineStr"/>
+      <c r="G139" s="10" t="inlineStr"/>
+    </row>
+    <row r="140" ht="27" customHeight="1">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="B140" s="12" t="inlineStr">
+        <is>
+          <t>Set cycle live</t>
+        </is>
+      </c>
+      <c r="C140" s="12" t="inlineStr">
+        <is>
+          <t>Open the cycle picker and set a different cycle as Live</t>
+        </is>
+      </c>
+      <c r="D140" s="12" t="inlineStr">
+        <is>
+          <t>Only the selected cycle is now live. The previous live cycle is no longer marked live. Header batch label updates</t>
+        </is>
+      </c>
+      <c r="E140" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="inlineStr"/>
+      <c r="G140" s="13" t="inlineStr"/>
+    </row>
+    <row r="141" ht="27" customHeight="1">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>Archive toggle</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t>Toggle the show/hide archived batches option in the cycle picker</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>Archived (past) cycles appear or disappear from the list. The toggle state is reflected correctly</t>
+        </is>
+      </c>
+      <c r="E141" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F141" s="9" t="inlineStr"/>
+      <c r="G141" s="10" t="inlineStr"/>
+    </row>
+    <row r="142" ht="27" customHeight="1">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="B142" s="12" t="inlineStr">
+        <is>
+          <t>Meal allowance toggle</t>
+        </is>
+      </c>
+      <c r="C142" s="12" t="inlineStr">
+        <is>
+          <t>Toggle meal allowance on for the current cycle</t>
+        </is>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>Meal timer appears on reservist check-in screen. Meal eligibility badge appears in the admin log after 6h work. Toast: "Meal allowance forms activated."</t>
+        </is>
+      </c>
+      <c r="E142" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="inlineStr"/>
+      <c r="G142" s="13" t="inlineStr"/>
+    </row>
+    <row r="143" ht="27" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>Cycle notice (broadcast)</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
+        <is>
+          <t>Post a notice for the current cycle</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>Notice appears as a banner on every reservist's check-in screen (scoped to that department). Toast: "Notice posted to all reservists."</t>
+        </is>
+      </c>
+      <c r="E143" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F143" s="9" t="inlineStr"/>
+      <c r="G143" s="10" t="inlineStr"/>
+    </row>
+    <row r="144" ht="27" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="inlineStr">
+        <is>
+          <t>Bulk no-report days</t>
+        </is>
+      </c>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>Paste multiple dates in dd/mm/yyyy format and apply them as no-report days</t>
+        </is>
+      </c>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
+          <t>Valid dates within the cycle are added. Dates outside the cycle range are ignored. Toast reports count added</t>
+        </is>
+      </c>
+      <c r="E144" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="inlineStr"/>
+      <c r="G144" s="13" t="inlineStr"/>
+    </row>
+    <row r="145" ht="27" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>Jump to date</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
+        <is>
+          <t>Use the date jump field to navigate to a specific date in a different cycle</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>Active cycle switches to the one containing that date. View offset is set correctly. Attendance for that date loads</t>
+        </is>
+      </c>
+      <c r="E145" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="inlineStr"/>
+      <c r="G145" s="10" t="inlineStr"/>
+    </row>
+    <row r="146" ht="6" customHeight="1"/>
+    <row r="147" ht="13.5" customHeight="1">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10. EXPORT AND REPORTS</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="n"/>
+      <c r="C147" s="5" t="n"/>
+      <c r="D147" s="5" t="n"/>
+      <c r="E147" s="5" t="n"/>
+      <c r="F147" s="5" t="n"/>
+      <c r="G147" s="5" t="n"/>
+    </row>
+    <row r="148" ht="27" customHeight="1">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>Export XLS - data integrity</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>Export attendance for a cycle with known data and open in Excel</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>All dates, names, statuses (P/MC/A), totals, and rate percentages are correct. No-report days and public holidays are excluded. Admin-corrected records show P*</t>
+        </is>
+      </c>
+      <c r="E148" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F148" s="9" t="inlineStr"/>
+      <c r="G148" s="10" t="inlineStr"/>
+    </row>
+    <row r="149" ht="27" customHeight="1">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="B149" s="12" t="inlineStr">
+        <is>
+          <t>Export XLS - empty cycle</t>
+        </is>
+      </c>
+      <c r="C149" s="12" t="inlineStr">
+        <is>
+          <t>Attempt to export a cycle with no reservists</t>
+        </is>
+      </c>
+      <c r="D149" s="12" t="inlineStr">
+        <is>
+          <t>Error toast: "No reservists found in this cycle." No file is downloaded</t>
+        </is>
+      </c>
+      <c r="E149" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F149" s="9" t="inlineStr"/>
+      <c r="G149" s="13" t="inlineStr"/>
+    </row>
+    <row r="150" ht="27" customHeight="1">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>Export XLS - headers freeze</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="inlineStr">
+        <is>
+          <t>Open the exported Excel file and scroll down past the header row</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>The title and column header rows remain visible (frozen panes). Row heights are consistent. Legend and Meal column present</t>
+        </is>
+      </c>
+      <c r="E150" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F150" s="9" t="inlineStr"/>
+      <c r="G150" s="10" t="inlineStr"/>
+    </row>
+    <row r="151" ht="27" customHeight="1">
+      <c r="A151" s="11" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
       </c>
-      <c r="B116" s="12" t="inlineStr">
+      <c r="B151" s="12" t="inlineStr">
+        <is>
+          <t>Print report preview</t>
+        </is>
+      </c>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>Open the Print/PDF report for a cycle with attendance data</t>
+        </is>
+      </c>
+      <c r="D151" s="12" t="inlineStr">
+        <is>
+          <t>Modal opens with formatted report showing all personnel, dates, status codes, summary stats including Meal column. Print button opens browser print dialog</t>
+        </is>
+      </c>
+      <c r="E151" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F151" s="9" t="inlineStr"/>
+      <c r="G151" s="13" t="inlineStr"/>
+    </row>
+    <row r="152" ht="27" customHeight="1">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="B152" s="7" t="inlineStr">
+        <is>
+          <t>Person history export</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="inlineStr">
+        <is>
+          <t>Open a person's history and export it to XLS</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>File downloads with name, date, status, in time, out time, and admin-correction flag for each row</t>
+        </is>
+      </c>
+      <c r="E152" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr"/>
+      <c r="G152" s="10" t="inlineStr"/>
+    </row>
+    <row r="153" ht="27" customHeight="1">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="inlineStr">
+        <is>
+          <t>WhatsApp share</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="inlineStr">
+        <is>
+          <t>Tap the WhatsApp share button from the overview tab</t>
+        </is>
+      </c>
+      <c r="D153" s="12" t="inlineStr">
+        <is>
+          <t>Pre-filled attendance summary opens in WhatsApp (or wa.me link). Message contains today's date, present/MC/absent counts, and list of names</t>
+        </is>
+      </c>
+      <c r="E153" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr"/>
+      <c r="G153" s="13" t="inlineStr"/>
+    </row>
+    <row r="154" ht="6" customHeight="1"/>
+    <row r="155" ht="13.5" customHeight="1">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  11. ACCOUNT MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="n"/>
+      <c r="C155" s="5" t="n"/>
+      <c r="D155" s="5" t="n"/>
+      <c r="E155" s="5" t="n"/>
+      <c r="F155" s="5" t="n"/>
+      <c r="G155" s="5" t="n"/>
+    </row>
+    <row r="156" ht="27" customHeight="1">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="B156" s="7" t="inlineStr">
+        <is>
+          <t>Change display name</t>
+        </is>
+      </c>
+      <c r="C156" s="7" t="inlineStr">
+        <is>
+          <t>Change the display name from account settings</t>
+        </is>
+      </c>
+      <c r="D156" s="7" t="inlineStr">
+        <is>
+          <t>Name updates in the header chip and in DB. Toast: "Display name updated."</t>
+        </is>
+      </c>
+      <c r="E156" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F156" s="9" t="inlineStr"/>
+      <c r="G156" s="10" t="inlineStr"/>
+    </row>
+    <row r="157" ht="27" customHeight="1">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="B157" s="12" t="inlineStr">
+        <is>
+          <t>Change password</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>Change password with correct current password and a matching new password (min 6 chars)</t>
+        </is>
+      </c>
+      <c r="D157" s="12" t="inlineStr">
+        <is>
+          <t>Toast: "Password updated." New password works on next login. Old password no longer works</t>
+        </is>
+      </c>
+      <c r="E157" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F157" s="9" t="inlineStr"/>
+      <c r="G157" s="13" t="inlineStr"/>
+    </row>
+    <row r="158" ht="27" customHeight="1">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t>Change password - wrong current</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="inlineStr">
+        <is>
+          <t>Attempt to change password with an incorrect current password</t>
+        </is>
+      </c>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
+          <t>Error: "Current password is incorrect." Password is not changed</t>
+        </is>
+      </c>
+      <c r="E158" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F158" s="9" t="inlineStr"/>
+      <c r="G158" s="10" t="inlineStr"/>
+    </row>
+    <row r="159" ht="27" customHeight="1">
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="B159" s="12" t="inlineStr">
         <is>
           <t>Upload profile photo</t>
         </is>
       </c>
-      <c r="C116" s="12" t="inlineStr">
-        <is>
-          <t>Upload a profile photo under 5 MB from account settings</t>
-        </is>
-      </c>
-      <c r="D116" s="12" t="inlineStr">
-        <is>
-          <t>Avatar updates immediately (optimistic). Uploaded to cloud storage. Toast: "Photo saved." Avatar persists on next login</t>
-        </is>
-      </c>
-      <c r="E116" s="15" t="inlineStr">
+      <c r="C159" s="12" t="inlineStr">
+        <is>
+          <t>Upload a profile photo under 20 MB from account settings</t>
+        </is>
+      </c>
+      <c r="D159" s="12" t="inlineStr">
+        <is>
+          <t>Avatar updates immediately (optimistic). Uploaded to cloud storage. Toast: "Profile photo updated." Avatar persists on next login</t>
+        </is>
+      </c>
+      <c r="E159" s="15" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F116" s="9" t="inlineStr"/>
-      <c r="G116" s="13" t="inlineStr"/>
-    </row>
-    <row r="117" ht="27" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="B117" s="7" t="inlineStr">
-        <is>
-          <t>Upload photo - over 5 MB</t>
-        </is>
-      </c>
-      <c r="C117" s="7" t="inlineStr">
-        <is>
-          <t>Attempt to upload a photo file larger than 5 MB</t>
-        </is>
-      </c>
-      <c r="D117" s="7" t="inlineStr">
-        <is>
-          <t>Error: "Photo must be under 5 MB." No upload is attempted</t>
-        </is>
-      </c>
-      <c r="E117" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F117" s="9" t="inlineStr"/>
-      <c r="G117" s="10" t="inlineStr"/>
-    </row>
-    <row r="118" ht="27" customHeight="1">
-      <c r="A118" s="11" t="inlineStr">
-        <is>
-          <t>10.6</t>
-        </is>
-      </c>
-      <c r="B118" s="12" t="inlineStr">
+      <c r="F159" s="9" t="inlineStr"/>
+      <c r="G159" s="13" t="inlineStr"/>
+    </row>
+    <row r="160" ht="27" customHeight="1">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t>Upload photo - over 20 MB</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="inlineStr">
+        <is>
+          <t>Attempt to upload a photo file larger than 20 MB</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>Error: "Photo must be under 20 MB." No upload is attempted</t>
+        </is>
+      </c>
+      <c r="E160" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F160" s="9" t="inlineStr"/>
+      <c r="G160" s="10" t="inlineStr"/>
+    </row>
+    <row r="161" ht="27" customHeight="1">
+      <c r="A161" s="11" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="B161" s="12" t="inlineStr">
+        <is>
+          <t>Tap own photo - lightbox</t>
+        </is>
+      </c>
+      <c r="C161" s="12" t="inlineStr">
+        <is>
+          <t>Tap the profile photo shown in account settings or the header chip</t>
+        </is>
+      </c>
+      <c r="D161" s="12" t="inlineStr">
+        <is>
+          <t>Photo opens in an enlarged lightbox overlay. Tapping outside the photo closes it</t>
+        </is>
+      </c>
+      <c r="E161" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F161" s="9" t="inlineStr"/>
+      <c r="G161" s="13" t="inlineStr"/>
+    </row>
+    <row r="162" ht="27" customHeight="1">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>11.7</t>
+        </is>
+      </c>
+      <c r="B162" s="7" t="inlineStr">
         <is>
           <t>Remove profile photo</t>
         </is>
       </c>
-      <c r="C118" s="12" t="inlineStr">
+      <c r="C162" s="7" t="inlineStr">
         <is>
           <t>Remove the profile photo from account settings</t>
         </is>
       </c>
-      <c r="D118" s="12" t="inlineStr">
+      <c r="D162" s="7" t="inlineStr">
         <is>
           <t>Avatar is removed from the UI and from cloud storage. Initials placeholder shows instead. Toast: "Profile photo removed."</t>
         </is>
       </c>
-      <c r="E118" s="15" t="inlineStr">
+      <c r="E162" s="15" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F118" s="9" t="inlineStr"/>
-      <c r="G118" s="13" t="inlineStr"/>
-    </row>
-    <row r="119" ht="27" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>10.7</t>
-        </is>
-      </c>
-      <c r="B119" s="7" t="inlineStr">
+      <c r="F162" s="9" t="inlineStr"/>
+      <c r="G162" s="10" t="inlineStr"/>
+    </row>
+    <row r="163" ht="27" customHeight="1">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="B163" s="12" t="inlineStr">
         <is>
           <t>Delete account</t>
         </is>
       </c>
-      <c r="C119" s="7" t="inlineStr">
+      <c r="C163" s="12" t="inlineStr">
         <is>
           <t>Delete account from account settings while online</t>
         </is>
       </c>
-      <c r="D119" s="7" t="inlineStr">
+      <c r="D163" s="12" t="inlineStr">
         <is>
           <t>Account deactivated in DB. Logged out. Login screen shows deletion confirmation banner. Account no longer accessible</t>
         </is>
       </c>
-      <c r="E119" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F119" s="9" t="inlineStr"/>
-      <c r="G119" s="10" t="inlineStr"/>
-    </row>
-    <row r="120" ht="27" customHeight="1">
-      <c r="A120" s="11" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="B120" s="12" t="inlineStr">
+      <c r="E163" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F163" s="9" t="inlineStr"/>
+      <c r="G163" s="13" t="inlineStr"/>
+    </row>
+    <row r="164" ht="27" customHeight="1">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="B164" s="7" t="inlineStr">
         <is>
           <t>Delete account - offline</t>
         </is>
       </c>
-      <c r="C120" s="12" t="inlineStr">
+      <c r="C164" s="7" t="inlineStr">
         <is>
           <t>Attempt to delete account while the device is offline</t>
         </is>
       </c>
-      <c r="D120" s="12" t="inlineStr">
+      <c r="D164" s="7" t="inlineStr">
         <is>
           <t>Error: "No connection. Cannot delete account while offline." Account is not deleted</t>
         </is>
       </c>
-      <c r="E120" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="inlineStr"/>
-      <c r="G120" s="13" t="inlineStr"/>
-    </row>
-    <row r="121" ht="6" customHeight="1"/>
-    <row r="122" ht="13.5" customHeight="1">
-      <c r="A122" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  11. PWA AND OFFLINE BEHAVIOUR</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="n"/>
-      <c r="C122" s="5" t="n"/>
-      <c r="D122" s="5" t="n"/>
-      <c r="E122" s="5" t="n"/>
-      <c r="F122" s="5" t="n"/>
-      <c r="G122" s="5" t="n"/>
-    </row>
-    <row r="123" ht="27" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="B123" s="7" t="inlineStr">
+      <c r="E164" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F164" s="9" t="inlineStr"/>
+      <c r="G164" s="10" t="inlineStr"/>
+    </row>
+    <row r="165" ht="6" customHeight="1"/>
+    <row r="166" ht="13.5" customHeight="1">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  12. CALENDAR DISPLAY (RESERVIST)</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="n"/>
+      <c r="C166" s="5" t="n"/>
+      <c r="D166" s="5" t="n"/>
+      <c r="E166" s="5" t="n"/>
+      <c r="F166" s="5" t="n"/>
+      <c r="G166" s="5" t="n"/>
+    </row>
+    <row r="167" ht="27" customHeight="1">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>Present days</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="inlineStr">
+        <is>
+          <t>View the attendance calendar for a day where the reservist has a Present status</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>Day cell is coloured green</t>
+        </is>
+      </c>
+      <c r="E167" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F167" s="9" t="inlineStr"/>
+      <c r="G167" s="10" t="inlineStr"/>
+    </row>
+    <row r="168" ht="27" customHeight="1">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B168" s="12" t="inlineStr">
+        <is>
+          <t>MC days</t>
+        </is>
+      </c>
+      <c r="C168" s="12" t="inlineStr">
+        <is>
+          <t>View the attendance calendar for a day with an MC status</t>
+        </is>
+      </c>
+      <c r="D168" s="12" t="inlineStr">
+        <is>
+          <t>Day cell is amber with a solid border</t>
+        </is>
+      </c>
+      <c r="E168" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F168" s="9" t="inlineStr"/>
+      <c r="G168" s="13" t="inlineStr"/>
+    </row>
+    <row r="169" ht="27" customHeight="1">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>Approved future MC</t>
+        </is>
+      </c>
+      <c r="C169" s="7" t="inlineStr">
+        <is>
+          <t>Admin approves an MC request for a future date; reservist views their calendar</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>Future date cell is amber with a solid border (same style as a past MC day)</t>
+        </is>
+      </c>
+      <c r="E169" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F169" s="9" t="inlineStr"/>
+      <c r="G169" s="10" t="inlineStr"/>
+    </row>
+    <row r="170" ht="27" customHeight="1">
+      <c r="A170" s="11" t="inlineStr">
+        <is>
+          <t>12.4</t>
+        </is>
+      </c>
+      <c r="B170" s="12" t="inlineStr">
+        <is>
+          <t>Pending future MC</t>
+        </is>
+      </c>
+      <c r="C170" s="12" t="inlineStr">
+        <is>
+          <t>Reservist has submitted an MC request that is still pending; views their calendar</t>
+        </is>
+      </c>
+      <c r="D170" s="12" t="inlineStr">
+        <is>
+          <t>Future date cell has a lighter amber tint with a dashed border, distinguishing it from an approved MC</t>
+        </is>
+      </c>
+      <c r="E170" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F170" s="9" t="inlineStr"/>
+      <c r="G170" s="13" t="inlineStr"/>
+    </row>
+    <row r="171" ht="27" customHeight="1">
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>Approved future Personal Leave</t>
+        </is>
+      </c>
+      <c r="C171" s="7" t="inlineStr">
+        <is>
+          <t>Admin approves a Personal Leave request for a future date; reservist views their calendar</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>Future date cell is red with a solid border</t>
+        </is>
+      </c>
+      <c r="E171" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F171" s="9" t="inlineStr"/>
+      <c r="G171" s="10" t="inlineStr"/>
+    </row>
+    <row r="172" ht="27" customHeight="1">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="B172" s="12" t="inlineStr">
+        <is>
+          <t>Pending future Personal Leave</t>
+        </is>
+      </c>
+      <c r="C172" s="12" t="inlineStr">
+        <is>
+          <t>Reservist has submitted a Personal Leave request still pending; views their calendar</t>
+        </is>
+      </c>
+      <c r="D172" s="12" t="inlineStr">
+        <is>
+          <t>Future date cell has a lighter red tint with a dashed border</t>
+        </is>
+      </c>
+      <c r="E172" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F172" s="9" t="inlineStr"/>
+      <c r="G172" s="13" t="inlineStr"/>
+    </row>
+    <row r="173" ht="27" customHeight="1">
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>No-report days</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="inlineStr">
+        <is>
+          <t>View the calendar on a day marked as a no-report day</t>
+        </is>
+      </c>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>Day cell is slate blue</t>
+        </is>
+      </c>
+      <c r="E173" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F173" s="9" t="inlineStr"/>
+      <c r="G173" s="10" t="inlineStr"/>
+    </row>
+    <row r="174" ht="27" customHeight="1">
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="B174" s="12" t="inlineStr">
+        <is>
+          <t>Absent days</t>
+        </is>
+      </c>
+      <c r="C174" s="12" t="inlineStr">
+        <is>
+          <t>View the calendar for a day where the reservist was marked absent</t>
+        </is>
+      </c>
+      <c r="D174" s="12" t="inlineStr">
+        <is>
+          <t>Day cell is red</t>
+        </is>
+      </c>
+      <c r="E174" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F174" s="9" t="inlineStr"/>
+      <c r="G174" s="13" t="inlineStr"/>
+    </row>
+    <row r="175" ht="27" customHeight="1">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="B175" s="7" t="inlineStr">
+        <is>
+          <t>Missing clock-out</t>
+        </is>
+      </c>
+      <c r="C175" s="7" t="inlineStr">
+        <is>
+          <t>View the calendar for a day the reservist was present but has no Phase 4 time</t>
+        </is>
+      </c>
+      <c r="D175" s="7" t="inlineStr">
+        <is>
+          <t>Day cell is orange with a dashed border</t>
+        </is>
+      </c>
+      <c r="E175" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F175" s="9" t="inlineStr"/>
+      <c r="G175" s="10" t="inlineStr"/>
+    </row>
+    <row r="176" ht="27" customHeight="1">
+      <c r="A176" s="11" t="inlineStr">
+        <is>
+          <t>12.10</t>
+        </is>
+      </c>
+      <c r="B176" s="12" t="inlineStr">
+        <is>
+          <t>Day detail panel</t>
+        </is>
+      </c>
+      <c r="C176" s="12" t="inlineStr">
+        <is>
+          <t>Tap any calendar day (present, absent, MC, leave, no-report, missing clock-out)</t>
+        </is>
+      </c>
+      <c r="D176" s="12" t="inlineStr">
+        <is>
+          <t>Detail panel appears with correct label, sub-text, and colour matching the day's status. Tapping outside dismisses it</t>
+        </is>
+      </c>
+      <c r="E176" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F176" s="9" t="inlineStr"/>
+      <c r="G176" s="13" t="inlineStr"/>
+    </row>
+    <row r="177" ht="6" customHeight="1"/>
+    <row r="178" ht="13.5" customHeight="1">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  13. INFO TAB (RESERVIST)</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="n"/>
+      <c r="C178" s="5" t="n"/>
+      <c r="D178" s="5" t="n"/>
+      <c r="E178" s="5" t="n"/>
+      <c r="F178" s="5" t="n"/>
+      <c r="G178" s="5" t="n"/>
+    </row>
+    <row r="179" ht="27" customHeight="1">
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>Shift info</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>Log in as a reservist and view the Info tab</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>Shift title, phase windows (0900, 1200, 1400, 1800 for Ops), attire, and relevant info items are displayed correctly</t>
+        </is>
+      </c>
+      <c r="E179" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F179" s="9" t="inlineStr"/>
+      <c r="G179" s="10" t="inlineStr"/>
+    </row>
+    <row r="180" ht="27" customHeight="1">
+      <c r="A180" s="11" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="B180" s="12" t="inlineStr">
+        <is>
+          <t>Meal allowance banner</t>
+        </is>
+      </c>
+      <c r="C180" s="12" t="inlineStr">
+        <is>
+          <t>View the Info tab when meal allowance is active vs. when it is off</t>
+        </is>
+      </c>
+      <c r="D180" s="12" t="inlineStr">
+        <is>
+          <t>Banner shows the active state when meal allowance is on, and an on-hold/inactive state when off</t>
+        </is>
+      </c>
+      <c r="E180" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F180" s="9" t="inlineStr"/>
+      <c r="G180" s="13" t="inlineStr"/>
+    </row>
+    <row r="181" ht="27" customHeight="1">
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>Team directory - batchmates only</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr">
+        <is>
+          <t>View the team directory section of the Info tab</t>
+        </is>
+      </c>
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>Only other reservists in the same batch are listed. The logged-in user is not shown. Admins are not shown</t>
+        </is>
+      </c>
+      <c r="E181" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F181" s="9" t="inlineStr"/>
+      <c r="G181" s="10" t="inlineStr"/>
+    </row>
+    <row r="182" ht="27" customHeight="1">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="B182" s="12" t="inlineStr">
+        <is>
+          <t>Contact number copy</t>
+        </is>
+      </c>
+      <c r="C182" s="12" t="inlineStr">
+        <is>
+          <t>Tap a batchmate's phone number in the team directory</t>
+        </is>
+      </c>
+      <c r="D182" s="12" t="inlineStr">
+        <is>
+          <t>Number is copied to the clipboard. Toast: "Copied to clipboard."</t>
+        </is>
+      </c>
+      <c r="E182" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F182" s="9" t="inlineStr"/>
+      <c r="G182" s="13" t="inlineStr"/>
+    </row>
+    <row r="183" ht="27" customHeight="1">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="B183" s="7" t="inlineStr">
+        <is>
+          <t>WhatsApp contact link</t>
+        </is>
+      </c>
+      <c r="C183" s="7" t="inlineStr">
+        <is>
+          <t>Tap the WhatsApp icon next to a batchmate's number</t>
+        </is>
+      </c>
+      <c r="D183" s="7" t="inlineStr">
+        <is>
+          <t>WhatsApp opens (or wa.me link is followed) with the correct pre-filled number</t>
+        </is>
+      </c>
+      <c r="E183" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F183" s="9" t="inlineStr"/>
+      <c r="G183" s="10" t="inlineStr"/>
+    </row>
+    <row r="184" ht="27" customHeight="1">
+      <c r="A184" s="11" t="inlineStr">
+        <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="B184" s="12" t="inlineStr">
+        <is>
+          <t>WA group link conditional</t>
+        </is>
+      </c>
+      <c r="C184" s="12" t="inlineStr">
+        <is>
+          <t>View the Info tab when the wa-group-link config is set vs. when it is blank</t>
+        </is>
+      </c>
+      <c r="D184" s="12" t="inlineStr">
+        <is>
+          <t>WA group link button is shown when configured and hidden when the config value is empty</t>
+        </is>
+      </c>
+      <c r="E184" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F184" s="9" t="inlineStr"/>
+      <c r="G184" s="13" t="inlineStr"/>
+    </row>
+    <row r="185" ht="6" customHeight="1"/>
+    <row r="186" ht="13.5" customHeight="1">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  14. PWA AND OFFLINE BEHAVIOUR</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="n"/>
+      <c r="C186" s="5" t="n"/>
+      <c r="D186" s="5" t="n"/>
+      <c r="E186" s="5" t="n"/>
+      <c r="F186" s="5" t="n"/>
+      <c r="G186" s="5" t="n"/>
+    </row>
+    <row r="187" ht="27" customHeight="1">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="B187" s="7" t="inlineStr">
         <is>
           <t>Install to home screen (iOS)</t>
         </is>
       </c>
-      <c r="C123" s="7" t="inlineStr">
+      <c r="C187" s="7" t="inlineStr">
         <is>
           <t>On iPhone, tap Share then "Add to Home Screen"</t>
         </is>
       </c>
-      <c r="D123" s="7" t="inlineStr">
+      <c r="D187" s="7" t="inlineStr">
         <is>
           <t>App icon appears on home screen. Opening it launches in standalone mode (no browser chrome)</t>
         </is>
       </c>
-      <c r="E123" s="15" t="inlineStr">
+      <c r="E187" s="15" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F123" s="9" t="inlineStr"/>
-      <c r="G123" s="10" t="inlineStr"/>
-    </row>
-    <row r="124" ht="27" customHeight="1">
-      <c r="A124" s="11" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="B124" s="12" t="inlineStr">
+      <c r="F187" s="9" t="inlineStr"/>
+      <c r="G187" s="10" t="inlineStr"/>
+    </row>
+    <row r="188" ht="27" customHeight="1">
+      <c r="A188" s="11" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="B188" s="12" t="inlineStr">
         <is>
           <t>Install to home screen (Android)</t>
         </is>
       </c>
-      <c r="C124" s="12" t="inlineStr">
+      <c r="C188" s="12" t="inlineStr">
         <is>
           <t>On Android, tap the install banner or browser menu "Add to Home Screen"</t>
         </is>
       </c>
-      <c r="D124" s="12" t="inlineStr">
+      <c r="D188" s="12" t="inlineStr">
         <is>
           <t>App icon appears on home screen. Launches in standalone mode</t>
         </is>
       </c>
-      <c r="E124" s="15" t="inlineStr">
+      <c r="E188" s="15" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F124" s="9" t="inlineStr"/>
-      <c r="G124" s="13" t="inlineStr"/>
-    </row>
-    <row r="125" ht="27" customHeight="1">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
-      <c r="B125" s="7" t="inlineStr">
+      <c r="F188" s="9" t="inlineStr"/>
+      <c r="G188" s="13" t="inlineStr"/>
+    </row>
+    <row r="189" ht="27" customHeight="1">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="B189" s="7" t="inlineStr">
         <is>
           <t>Offline page load</t>
         </is>
       </c>
-      <c r="C125" s="7" t="inlineStr">
+      <c r="C189" s="7" t="inlineStr">
         <is>
           <t>Open the app with no internet connection (after one prior online load to prime the cache)</t>
         </is>
       </c>
-      <c r="D125" s="7" t="inlineStr">
+      <c r="D189" s="7" t="inlineStr">
         <is>
           <t>App loads from service worker cache. Offline badge is shown. Last known state is displayed</t>
         </is>
       </c>
-      <c r="E125" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F125" s="9" t="inlineStr"/>
-      <c r="G125" s="10" t="inlineStr"/>
-    </row>
-    <row r="126" ht="27" customHeight="1">
-      <c r="A126" s="11" t="inlineStr">
-        <is>
-          <t>11.4</t>
-        </is>
-      </c>
-      <c r="B126" s="12" t="inlineStr">
+      <c r="E189" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F189" s="9" t="inlineStr"/>
+      <c r="G189" s="10" t="inlineStr"/>
+    </row>
+    <row r="190" ht="27" customHeight="1">
+      <c r="A190" s="11" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="B190" s="12" t="inlineStr">
         <is>
           <t>A2HS prompt (first visit)</t>
         </is>
       </c>
-      <c r="C126" s="12" t="inlineStr">
+      <c r="C190" s="12" t="inlineStr">
         <is>
           <t>Visit the app for the first time on a mobile device that supports A2HS</t>
         </is>
       </c>
-      <c r="D126" s="12" t="inlineStr">
+      <c r="D190" s="12" t="inlineStr">
         <is>
           <t>Add-to-Home-Screen prompt appears after 30 seconds. Dismissing stores the preference so it does not re-appear within 24 hours</t>
         </is>
       </c>
-      <c r="E126" s="15" t="inlineStr">
+      <c r="E190" s="15" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F126" s="9" t="inlineStr"/>
-      <c r="G126" s="13" t="inlineStr"/>
-    </row>
-    <row r="127" ht="27" customHeight="1">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="B127" s="7" t="inlineStr">
+      <c r="F190" s="9" t="inlineStr"/>
+      <c r="G190" s="13" t="inlineStr"/>
+    </row>
+    <row r="191" ht="27" customHeight="1">
+      <c r="A191" s="6" t="inlineStr">
+        <is>
+          <t>14.5</t>
+        </is>
+      </c>
+      <c r="B191" s="7" t="inlineStr">
         <is>
           <t>Landscape orientation warning</t>
         </is>
       </c>
-      <c r="C127" s="7" t="inlineStr">
+      <c r="C191" s="7" t="inlineStr">
         <is>
           <t>Rotate a mobile device to landscape orientation</t>
         </is>
       </c>
-      <c r="D127" s="7" t="inlineStr">
+      <c r="D191" s="7" t="inlineStr">
         <is>
           <t>Overlay appears: "Please rotate your device to portrait mode." App is unusable in landscape. Rotating back dismisses the overlay</t>
         </is>
       </c>
-      <c r="E127" s="15" t="inlineStr">
+      <c r="E191" s="15" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F127" s="9" t="inlineStr"/>
-      <c r="G127" s="10" t="inlineStr"/>
-    </row>
-    <row r="128" ht="27" customHeight="1">
-      <c r="A128" s="11" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
-      </c>
-      <c r="B128" s="12" t="inlineStr">
+      <c r="F191" s="9" t="inlineStr"/>
+      <c r="G191" s="10" t="inlineStr"/>
+    </row>
+    <row r="192" ht="27" customHeight="1">
+      <c r="A192" s="11" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="B192" s="12" t="inlineStr">
         <is>
           <t>In-app browser warning</t>
         </is>
       </c>
-      <c r="C128" s="12" t="inlineStr">
+      <c r="C192" s="12" t="inlineStr">
         <is>
           <t>Open the app URL from within WhatsApp or Instagram</t>
         </is>
       </c>
-      <c r="D128" s="12" t="inlineStr">
+      <c r="D192" s="12" t="inlineStr">
         <is>
           <t>Warning displayed: GPS is blocked inside WhatsApp/Instagram. Instructions shown to open in Safari or Chrome</t>
         </is>
       </c>
-      <c r="E128" s="14" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F128" s="9" t="inlineStr"/>
-      <c r="G128" s="13" t="inlineStr"/>
-    </row>
-    <row r="129" ht="27" customHeight="1">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>11.7</t>
-        </is>
-      </c>
-      <c r="B129" s="7" t="inlineStr">
+      <c r="E192" s="14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F192" s="9" t="inlineStr"/>
+      <c r="G192" s="13" t="inlineStr"/>
+    </row>
+    <row r="193" ht="27" customHeight="1">
+      <c r="A193" s="6" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="B193" s="7" t="inlineStr">
         <is>
           <t>Tab visibility - idle auto-logout</t>
         </is>
       </c>
-      <c r="C129" s="7" t="inlineStr">
+      <c r="C193" s="7" t="inlineStr">
         <is>
           <t>Hide the app tab for 20+ minutes then restore it</t>
         </is>
       </c>
-      <c r="D129" s="7" t="inlineStr">
+      <c r="D193" s="7" t="inlineStr">
         <is>
           <t>On restore, elapsed time is checked. If over 20 minutes idle, the session is ended and the user is shown the login screen</t>
         </is>
       </c>
-      <c r="E129" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F129" s="9" t="inlineStr"/>
-      <c r="G129" s="10" t="inlineStr"/>
-    </row>
-    <row r="130" ht="6" customHeight="1"/>
+      <c r="E193" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F193" s="9" t="inlineStr"/>
+      <c r="G193" s="10" t="inlineStr"/>
+    </row>
+    <row r="194" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="15">
+    <mergeCell ref="A102:G102"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A88:G88"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A105:G105"/>
-    <mergeCell ref="A122:G122"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A136:G136"/>
+    <mergeCell ref="A155:G155"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A186:G186"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A96:G96"/>
-    <mergeCell ref="A112:G112"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A147:G147"/>
+    <mergeCell ref="A178:G178"/>
+    <mergeCell ref="A166:G166"/>
+    <mergeCell ref="A117:G117"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
